--- a/Luban/Config/Datas/#TreasureConfig.xlsx
+++ b/Luban/Config/Datas/#TreasureConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFABF367-ACF0-4034-A711-192087090357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6494870B-79D6-4A19-867F-1F8C5A8890F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="4290" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="1395" yWindow="1650" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -87,26 +87,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CalculateActionWheelMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>StartActionWheelMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AsTargetActionMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>BeforeClashMoment</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>UnderHitMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AfterClashMoment</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -131,18 +115,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>计算息的时候调用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>息开始扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>被作为目标时扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>释放成功后扳机</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -151,10 +123,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>命中后扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>交锋后扳机</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -168,6 +136,34 @@
   </si>
   <si>
     <t>ReleaseSkillActionMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=,),int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeActionMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeUnderActionMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AfterUnderActionMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到行动前调用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到行动后调用扳机</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -532,21 +528,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="8" width="41.25" customWidth="1"/>
-    <col min="9" max="9" width="24.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.75" customWidth="1"/>
-    <col min="13" max="13" width="16.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="41.25" customWidth="1"/>
+    <col min="8" max="8" width="24.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.75" customWidth="1"/>
+    <col min="11" max="11" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.5" customWidth="1"/>
+    <col min="14" max="14" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -560,43 +556,40 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" t="s">
-        <v>14</v>
-      </c>
       <c r="H1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" t="s">
         <v>15</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>16</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" t="s">
         <v>17</v>
       </c>
-      <c r="K1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>18</v>
       </c>
-      <c r="M1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P1" t="s">
-        <v>22</v>
-      </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -610,43 +603,40 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="F2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="H2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="J2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="K2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="M2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="N2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="O2" t="s">
-        <v>5</v>
-      </c>
-      <c r="P2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -660,43 +650,40 @@
         <v>9</v>
       </c>
       <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" t="s">
         <v>23</v>
       </c>
-      <c r="F3" t="s">
+      <c r="K3" t="s">
         <v>24</v>
       </c>
-      <c r="G3" t="s">
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" t="s">
         <v>25</v>
       </c>
-      <c r="H3" t="s">
+      <c r="O3" t="s">
         <v>26</v>
       </c>
-      <c r="I3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" t="s">
-        <v>33</v>
-      </c>
-      <c r="P3" t="s">
-        <v>34</v>
-      </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B4">
         <v>1</v>
       </c>
@@ -739,11 +726,8 @@
       <c r="O4">
         <v>1</v>
       </c>
-      <c r="P4">
-        <v>1</v>
-      </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>2</v>
       </c>
@@ -784,9 +768,6 @@
         <v>1</v>
       </c>
       <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
         <v>1</v>
       </c>
     </row>

--- a/Luban/Config/Datas/#TreasureConfig.xlsx
+++ b/Luban/Config/Datas/#TreasureConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6494870B-79D6-4A19-867F-1F8C5A8890F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1DC6B7-2338-41B9-A6BF-F6C3987E36EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1395" yWindow="1650" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="5340" yWindow="4800" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -171,7 +171,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -186,6 +186,13 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -210,9 +217,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -529,245 +539,247 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
   <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="7" width="41.25" customWidth="1"/>
-    <col min="8" max="8" width="24.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.75" customWidth="1"/>
-    <col min="11" max="11" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.5" customWidth="1"/>
-    <col min="14" max="14" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="7" width="41.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="24.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.75" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="18.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="E2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="1">
+        <v>1</v>
+      </c>
+      <c r="O4" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B5">
+      <c r="B5" s="1">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1">
         <v>1</v>
       </c>
     </row>

--- a/Luban/Config/Datas/#TreasureConfig.xlsx
+++ b/Luban/Config/Datas/#TreasureConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1DC6B7-2338-41B9-A6BF-F6C3987E36EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3355EFF4-A879-438F-BC6C-18D5318E47EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5340" yWindow="4800" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="39">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -164,6 +164,22 @@
   </si>
   <si>
     <t>受到行动后调用扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>息开始的扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionWheelStartMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CalculateActionWheelMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算息的时候扳机调用</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -171,7 +187,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,6 +209,12 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -217,11 +239,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -538,23 +563,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="7" width="41.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="24.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.75" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="18.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="20.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -573,35 +602,41 @@
       <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -620,7 +655,7 @@
       <c r="F2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -647,8 +682,14 @@
       <c r="O2" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="P2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -667,35 +708,41 @@
       <c r="F3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B4" s="1">
         <v>1</v>
       </c>
@@ -705,41 +752,8 @@
       <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="1">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1</v>
-      </c>
-      <c r="J4" s="1">
-        <v>1</v>
-      </c>
-      <c r="K4" s="1">
-        <v>1</v>
-      </c>
-      <c r="L4" s="1">
-        <v>1</v>
-      </c>
-      <c r="M4" s="1">
-        <v>1</v>
-      </c>
-      <c r="N4" s="1">
-        <v>1</v>
-      </c>
-      <c r="O4" s="1">
-        <v>1</v>
-      </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
         <v>2</v>
       </c>
@@ -748,39 +762,6 @@
       </c>
       <c r="D5" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1">
-        <v>1</v>
-      </c>
-      <c r="L5" s="1">
-        <v>1</v>
-      </c>
-      <c r="M5" s="1">
-        <v>1</v>
-      </c>
-      <c r="N5" s="1">
-        <v>1</v>
-      </c>
-      <c r="O5" s="1">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/#TreasureConfig.xlsx
+++ b/Luban/Config/Datas/#TreasureConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3355EFF4-A879-438F-BC6C-18D5318E47EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2267B25-A6EB-41C3-997E-0E46B1417071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -72,114 +72,6 @@
   </si>
   <si>
     <t>宝器2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DoDesitionMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleStartMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RoundStartMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BeforeClashMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AfterClashMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AfterActionMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RoundEndMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动决定后扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗开始扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合开始扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>释放成功后扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交锋前扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交锋后扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动后扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合结束扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ReleaseSkillActionMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(list#sep=,),int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BeforeActionMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BeforeUnderActionMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AfterUnderActionMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动前</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到行动前调用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到行动后调用扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>息开始的扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActionWheelStartMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CalculateActionWheelMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计算息的时候扳机调用</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -187,7 +79,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,12 +101,6 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -239,14 +125,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -563,27 +446,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="20.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="41.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="29.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="28" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="1"/>
+    <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -596,47 +465,8 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>18</v>
-      </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -649,47 +479,8 @@
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>28</v>
-      </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -702,47 +493,8 @@
       <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B4" s="1">
         <v>1</v>
       </c>
@@ -753,7 +505,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
         <v>2</v>
       </c>

--- a/Luban/Config/Datas/#TreasureConfig.xlsx
+++ b/Luban/Config/Datas/#TreasureConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2267B25-A6EB-41C3-997E-0E46B1417071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93828D32-B3EB-480B-8928-079F9029C47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -20,12 +20,21 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="506">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -35,14 +44,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>##type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -67,11 +68,1635 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>宝器1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>宝器2</t>
+    <t>猊殇</t>
+  </si>
+  <si>
+    <t>提供心法：猊煞变</t>
+  </si>
+  <si>
+    <t>奇异兽首造型的炁具护腕，暗红色的晶石兽瞳森冷如活物。此物能将注入的炁转化为源源不断的煞以供相关奇术的使用。非毒炼之躯承难以受煞之运转，何谈反复精进其派式奇术，而毒炼之躯本就煞已入炁——此物之矛盾，只是出于鬼匠对以器制煞的探索罢了。</t>
+  </si>
+  <si>
+    <t>角力觔</t>
+  </si>
+  <si>
+    <t>交锋时对手倍率不超过115%，且自身杀式的基础倍率低于目标0~5的百分比之间时，倍率增加5的百分比。该效果在行动和交锋失败共4次后可再次触发。</t>
+  </si>
+  <si>
+    <t>以某种精兽筋制成之物，乍看之下就是条皮绳。缚于手臂时在两股力量碰撞的催动之下将反而回激，一瞬辗碎对手架势。虽筋骨难以承受其撕扯般的代价，但野兽相争唯有势均力敌不可认败。</t>
+  </si>
+  <si>
+    <t>角力觔+1</t>
+  </si>
+  <si>
+    <t>交锋时对手倍率不超过120%，且自身杀式的基础倍率低于目标0~5的百分比之间时，倍率增加5的百分比。该效果在行动和交锋失败共4次后可再次触发。</t>
+  </si>
+  <si>
+    <t>角力觔+2</t>
+  </si>
+  <si>
+    <t>交锋时对手倍率不超过125%，且自身杀式的基础倍率低于目标0~5的百分比之间时，倍率增加5的百分比。该效果在行动和交锋失败共4次后可再次触发。</t>
+  </si>
+  <si>
+    <t>角力觔+3</t>
+  </si>
+  <si>
+    <t>交锋时对手倍率不超过130%，且自身杀式的基础倍率低于目标0~5的百分比之间时，倍率增加5的百分比。该效果在行动和交锋失败共4次后可再次触发。</t>
+  </si>
+  <si>
+    <t>角力觔+4</t>
+  </si>
+  <si>
+    <t>交锋时对手倍率不超过135%，且自身杀式的基础倍率低于目标0~5的百分比之间时，倍率增加5的百分比。该效果在行动和交锋失败共4次后可再次触发。</t>
+  </si>
+  <si>
+    <t>角力觔+5</t>
+  </si>
+  <si>
+    <t>交锋时对手倍率不超过140%，且自身杀式的基础倍率低于目标0~5的百分比之间时，倍率增加5的百分比。该效果在行动和交锋失败共4次后可再次触发。</t>
+  </si>
+  <si>
+    <t>角力觔+6</t>
+  </si>
+  <si>
+    <t>交锋时对手倍率不超过145%，且自身杀式的基础倍率低于目标0~5的百分比之间时，倍率增加5的百分比。该效果在行动和交锋失败共4次后可再次触发。</t>
+  </si>
+  <si>
+    <t>角力觔+7</t>
+  </si>
+  <si>
+    <t>交锋时对手倍率不超过150%，且自身杀式的基础倍率低于目标0~5的百分比之间时，倍率增加5的百分比。该效果在行动和交锋失败共4次后可再次触发。</t>
+  </si>
+  <si>
+    <t>角力觔+8</t>
+  </si>
+  <si>
+    <t>交锋时对手倍率不超过155%，且自身杀式的基础倍率低于目标0~5的百分比之间时，倍率增加5的百分比。该效果在行动和交锋失败共4次后可再次触发。</t>
+  </si>
+  <si>
+    <t>诛魔之器</t>
+  </si>
+  <si>
+    <t>诛魔之器+1</t>
+  </si>
+  <si>
+    <t>攻击精兽时倍率增加5百分比，对其造成的直接伤害整体提升15%</t>
+  </si>
+  <si>
+    <t>诛魔之器+2</t>
+  </si>
+  <si>
+    <t>攻击精兽时倍率增加5百分比，对其造成的直接伤害整体提升30%</t>
+  </si>
+  <si>
+    <t>诛魔之器+3</t>
+  </si>
+  <si>
+    <t>攻击精兽时倍率增加5百分比，对其造成的直接伤害整体提升45%</t>
+  </si>
+  <si>
+    <t>诛魔之器+4</t>
+  </si>
+  <si>
+    <t>攻击精兽时倍率增加5百分比，对其造成的直接伤害整体提升60%</t>
+  </si>
+  <si>
+    <t>诛魔之器+5</t>
+  </si>
+  <si>
+    <t>攻击精兽时倍率增加5百分比，对其造成的直接伤害整体提升75%</t>
+  </si>
+  <si>
+    <t>诛魔之器+6</t>
+  </si>
+  <si>
+    <t>攻击精兽时倍率增加5百分比，对其造成的直接伤害整体提升90%</t>
+  </si>
+  <si>
+    <t>诛魔之器+7</t>
+  </si>
+  <si>
+    <t>攻击精兽时倍率增加5百分比，对其造成的直接伤害整体提升105%</t>
+  </si>
+  <si>
+    <t>诛魔之器+8</t>
+  </si>
+  <si>
+    <t>攻击精兽时倍率增加5百分比，对其造成的直接伤害整体提升120%</t>
+  </si>
+  <si>
+    <t>魂霁</t>
+  </si>
+  <si>
+    <t>先师元定子所使用的道剑，据他本人所说此剑乃是元真门镇派至宝，也是由此元定子常自居元真门新掌门。</t>
+  </si>
+  <si>
+    <t>魂霁+1</t>
+  </si>
+  <si>
+    <t>魂霁+2</t>
+  </si>
+  <si>
+    <t>魂霁+3</t>
+  </si>
+  <si>
+    <t>魂霁+4</t>
+  </si>
+  <si>
+    <t>磬</t>
+  </si>
+  <si>
+    <t>使用法咒式后下一次武杀式命中后额外提升125+GR*1点伤害</t>
+  </si>
+  <si>
+    <t>使用法咒式后下一次武杀式命中后额外提升125+GR*2点伤害</t>
+  </si>
+  <si>
+    <t>使用法咒式后下一次武杀式命中后额外提升132+GR*2点伤害</t>
+  </si>
+  <si>
+    <t>使用法咒式后下一次武杀式命中后额外提升132+GR*3点伤害</t>
+  </si>
+  <si>
+    <t>使用法咒式后下一次武杀式命中后额外提升158+GR*3点伤害</t>
+  </si>
+  <si>
+    <t>使用法咒式后下一次武杀式命中后额外提升158+GR*4点伤害</t>
+  </si>
+  <si>
+    <t>使用法咒式后下一次武杀式命中后额外提升400+GR*4点伤害</t>
+  </si>
+  <si>
+    <t>使用法咒式后下一次武杀式命中后额外提升400+GR*5点伤害</t>
+  </si>
+  <si>
+    <t>使用法咒式后下一次武杀式命中后额外提升510+GR*5点伤害</t>
+  </si>
+  <si>
+    <t>被包裹的剑</t>
+  </si>
+  <si>
+    <t>宫山传位剑</t>
+  </si>
+  <si>
+    <t>抚赭金刚伞</t>
+  </si>
+  <si>
+    <t>回合结束时未承受过攻击则护体状态不会扣除，回合开始时获得24层护体</t>
+  </si>
+  <si>
+    <t>抚赭金刚伞+1</t>
+  </si>
+  <si>
+    <t>回合结束时未承受过攻击则护体状态不会扣除，回合开始时获得54层护体</t>
+  </si>
+  <si>
+    <t>抚赭金刚伞+2</t>
+  </si>
+  <si>
+    <t>回合结束时未承受过攻击则护体状态不会扣除，回合开始时获得84层护体</t>
+  </si>
+  <si>
+    <t>抚赭金刚伞+3</t>
+  </si>
+  <si>
+    <t>回合结束时未承受过攻击则护体状态不会扣除，回合开始时获得127层护体</t>
+  </si>
+  <si>
+    <t>抚赭金刚伞+4</t>
+  </si>
+  <si>
+    <t>回合结束时未承受过攻击则护体状态不会扣除，回合开始时获得170层护体</t>
+  </si>
+  <si>
+    <t>抚赭金刚伞+5</t>
+  </si>
+  <si>
+    <t>回合结束时未承受过攻击则护体状态不会扣除，回合开始时获得225层护体</t>
+  </si>
+  <si>
+    <t>抚赭金刚伞+6</t>
+  </si>
+  <si>
+    <t>回合结束时未承受过攻击则护体状态不会扣除，回合开始时获得280层护体</t>
+  </si>
+  <si>
+    <t>抚赭金刚伞+7</t>
+  </si>
+  <si>
+    <t>回合结束时未承受过攻击则护体状态不会扣除，回合开始时获得390层护体</t>
+  </si>
+  <si>
+    <t>抚赭金刚伞+8</t>
+  </si>
+  <si>
+    <t>回合结束时未承受过攻击则护体状态不会扣除，回合开始时获得500层护体</t>
+  </si>
+  <si>
+    <t>流云霓裳</t>
+  </si>
+  <si>
+    <t>破,20</t>
+  </si>
+  <si>
+    <t>流云霓裳+1</t>
+  </si>
+  <si>
+    <t>破,44</t>
+  </si>
+  <si>
+    <t>流云霓裳+2</t>
+  </si>
+  <si>
+    <t>破,80</t>
+  </si>
+  <si>
+    <t>流云霓裳+3</t>
+  </si>
+  <si>
+    <t>破,136</t>
+  </si>
+  <si>
+    <t>流云霓裳+4</t>
+  </si>
+  <si>
+    <t>破,232</t>
+  </si>
+  <si>
+    <t>玉短刀</t>
+  </si>
+  <si>
+    <t>力,25</t>
+  </si>
+  <si>
+    <t>玉短刀+1</t>
+  </si>
+  <si>
+    <t>力,55</t>
+  </si>
+  <si>
+    <t>玉短刀+2</t>
+  </si>
+  <si>
+    <t>力,100</t>
+  </si>
+  <si>
+    <t>玉短刀+3</t>
+  </si>
+  <si>
+    <t>力,170</t>
+  </si>
+  <si>
+    <t>玉短刀+4</t>
+  </si>
+  <si>
+    <t>力,290</t>
+  </si>
+  <si>
+    <t>錾海石</t>
+  </si>
+  <si>
+    <t>技,25</t>
+  </si>
+  <si>
+    <t>錾海石+1</t>
+  </si>
+  <si>
+    <t>技,55</t>
+  </si>
+  <si>
+    <t>錾海石+2</t>
+  </si>
+  <si>
+    <t>技,100</t>
+  </si>
+  <si>
+    <t>錾海石+3</t>
+  </si>
+  <si>
+    <t>技,170</t>
+  </si>
+  <si>
+    <t>錾海石+4</t>
+  </si>
+  <si>
+    <t>技,290</t>
+  </si>
+  <si>
+    <t>陨铁钵</t>
+  </si>
+  <si>
+    <t>防,20</t>
+  </si>
+  <si>
+    <t>陨铁钵+1</t>
+  </si>
+  <si>
+    <t>防,44</t>
+  </si>
+  <si>
+    <t>陨铁钵+2</t>
+  </si>
+  <si>
+    <t>防,80</t>
+  </si>
+  <si>
+    <t>陨铁钵+3</t>
+  </si>
+  <si>
+    <t>防,136</t>
+  </si>
+  <si>
+    <t>陨铁钵+4</t>
+  </si>
+  <si>
+    <t>防,232</t>
+  </si>
+  <si>
+    <t>赤虎印</t>
+  </si>
+  <si>
+    <t>体,150</t>
+  </si>
+  <si>
+    <t>赤虎印+1</t>
+  </si>
+  <si>
+    <t>体,630</t>
+  </si>
+  <si>
+    <t>赤虎印+2</t>
+  </si>
+  <si>
+    <t>体,1290</t>
+  </si>
+  <si>
+    <t>赤虎印+3</t>
+  </si>
+  <si>
+    <t>体,2250</t>
+  </si>
+  <si>
+    <t>赤虎印+4</t>
+  </si>
+  <si>
+    <t>体,4050</t>
+  </si>
+  <si>
+    <t>燕笛</t>
+  </si>
+  <si>
+    <t>回合开始速+30，随机获得2个键。该效果每3个回合会触发一次。</t>
+  </si>
+  <si>
+    <t>燕笛+1</t>
+  </si>
+  <si>
+    <t>巧,2</t>
+  </si>
+  <si>
+    <t>回合开始速+38，随机获得2个键。该效果每3个回合会触发一次。</t>
+  </si>
+  <si>
+    <t>燕笛+2</t>
+  </si>
+  <si>
+    <t>巧,4</t>
+  </si>
+  <si>
+    <t>回合开始速+46，随机获得2个键。该效果每3个回合会触发一次。</t>
+  </si>
+  <si>
+    <t>燕笛+3</t>
+  </si>
+  <si>
+    <t>巧,6</t>
+  </si>
+  <si>
+    <t>回合开始速+57，随机获得2个键。该效果每3个回合会触发一次。</t>
+  </si>
+  <si>
+    <t>燕笛+4</t>
+  </si>
+  <si>
+    <t>巧,8</t>
+  </si>
+  <si>
+    <t>回合开始速+68，随机获得2个键。该效果每3个回合会触发一次。</t>
+  </si>
+  <si>
+    <t>燕笛+5</t>
+  </si>
+  <si>
+    <t>巧,11</t>
+  </si>
+  <si>
+    <t>回合开始速+84，随机获得2个键。该效果每3个回合会触发一次。</t>
+  </si>
+  <si>
+    <t>燕笛+6</t>
+  </si>
+  <si>
+    <t>巧,14</t>
+  </si>
+  <si>
+    <t>回合开始速+100，随机获得2个键。该效果每3个回合会触发一次。</t>
+  </si>
+  <si>
+    <t>燕笛+7</t>
+  </si>
+  <si>
+    <t>巧,17</t>
+  </si>
+  <si>
+    <t>回合开始速+130，随机获得2个键。该效果每3个回合会触发一次。</t>
+  </si>
+  <si>
+    <t>燕笛+8</t>
+  </si>
+  <si>
+    <t>巧,20</t>
+  </si>
+  <si>
+    <t>回合开始速+160，随机获得2个键。该效果每3个回合会触发一次。</t>
+  </si>
+  <si>
+    <t>xx的肩甲</t>
+  </si>
+  <si>
+    <t>力,25|技,25</t>
+  </si>
+  <si>
+    <t>回合开始随机消耗键直至不超过6个，每消耗一个键随机获得1层武增/术增/力增/技增</t>
+  </si>
+  <si>
+    <t>xx的肩甲+1</t>
+  </si>
+  <si>
+    <t>力,40|技,40</t>
+  </si>
+  <si>
+    <t>xx的肩甲+2</t>
+  </si>
+  <si>
+    <t>力,55|技,55</t>
+  </si>
+  <si>
+    <t>xx的肩甲+3</t>
+  </si>
+  <si>
+    <t>力,77.5|技,77.5</t>
+  </si>
+  <si>
+    <t>xx的肩甲+4</t>
+  </si>
+  <si>
+    <t>力,100|技,100</t>
+  </si>
+  <si>
+    <t>xx的肩甲+5</t>
+  </si>
+  <si>
+    <t>力,135|技,135</t>
+  </si>
+  <si>
+    <t>xx的肩甲+6</t>
+  </si>
+  <si>
+    <t>力,170|技,170</t>
+  </si>
+  <si>
+    <t>xx的肩甲+7</t>
+  </si>
+  <si>
+    <t>力,230|技,230</t>
+  </si>
+  <si>
+    <t>xx的肩甲+8</t>
+  </si>
+  <si>
+    <t>力,290|技,290</t>
+  </si>
+  <si>
+    <t>回合开始获得1层乱阵。行动后减少部分负面1层计数（3，8类）</t>
+  </si>
+  <si>
+    <t>防,5</t>
+  </si>
+  <si>
+    <t>战斗开始获得1层异鳞，回合结束获得1层异鳞</t>
+  </si>
+  <si>
+    <t>防,8</t>
+  </si>
+  <si>
+    <t>防,11</t>
+  </si>
+  <si>
+    <t>防,15.5</t>
+  </si>
+  <si>
+    <t>防,27</t>
+  </si>
+  <si>
+    <t>防,34</t>
+  </si>
+  <si>
+    <t>防,46</t>
+  </si>
+  <si>
+    <t>防,58</t>
+  </si>
+  <si>
+    <t>贪面</t>
+  </si>
+  <si>
+    <t>力,6|技,6</t>
+  </si>
+  <si>
+    <t>杀式造成直接伤害后获得等同伤害量的饕餮万物状态层数</t>
+  </si>
+  <si>
+    <t>贪面+1</t>
+  </si>
+  <si>
+    <t>力,10|技,10</t>
+  </si>
+  <si>
+    <t>贪面+2</t>
+  </si>
+  <si>
+    <t>力,14|技,14</t>
+  </si>
+  <si>
+    <t>贪面+3</t>
+  </si>
+  <si>
+    <t>力,19.5|技,19.5</t>
+  </si>
+  <si>
+    <t>贪面+4</t>
+  </si>
+  <si>
+    <t>贪面+5</t>
+  </si>
+  <si>
+    <t>力,33.5|技,33.5</t>
+  </si>
+  <si>
+    <t>贪面+6</t>
+  </si>
+  <si>
+    <t>力,44.5|技,44.5</t>
+  </si>
+  <si>
+    <t>贪面+7</t>
+  </si>
+  <si>
+    <t>力,57.5|技,57.5</t>
+  </si>
+  <si>
+    <t>贪面+8</t>
+  </si>
+  <si>
+    <t>力,72.5|技,72.5</t>
+  </si>
+  <si>
+    <t>祭皿</t>
+  </si>
+  <si>
+    <t>体,-150</t>
+  </si>
+  <si>
+    <t>杀式造成直接伤害后获得等同伤害量15%的血炁甲状态层数</t>
+  </si>
+  <si>
+    <t>祭皿+1</t>
+  </si>
+  <si>
+    <t>体,-630</t>
+  </si>
+  <si>
+    <t>杀式造成直接伤害后获得等同伤害量18%的血炁甲状态层数</t>
+  </si>
+  <si>
+    <t>祭皿+2</t>
+  </si>
+  <si>
+    <t>体,-1290</t>
+  </si>
+  <si>
+    <t>杀式造成直接伤害后获得等同伤害量21%的血炁甲状态层数</t>
+  </si>
+  <si>
+    <t>祭皿+3</t>
+  </si>
+  <si>
+    <t>体,-2250</t>
+  </si>
+  <si>
+    <t>杀式造成直接伤害后获得等同伤害量25%的血炁甲状态层数</t>
+  </si>
+  <si>
+    <t>祭皿+4</t>
+  </si>
+  <si>
+    <t>体,-4050</t>
+  </si>
+  <si>
+    <t>杀式造成直接伤害后获得等同伤害量30%的血炁甲状态层数</t>
+  </si>
+  <si>
+    <t>存储至多3个溢出的键，在回合开始时若键未到达持有上限则进行补充</t>
+  </si>
+  <si>
+    <t>每回合恢复25体</t>
+  </si>
+  <si>
+    <t>每回合恢复60体</t>
+  </si>
+  <si>
+    <t>每回合恢复95体</t>
+  </si>
+  <si>
+    <t>每回合恢复140体</t>
+  </si>
+  <si>
+    <t>每回合恢复185体</t>
+  </si>
+  <si>
+    <t>每回合恢复250体</t>
+  </si>
+  <si>
+    <t>每回合恢复315体</t>
+  </si>
+  <si>
+    <t>每回合恢复435体</t>
+  </si>
+  <si>
+    <t>每回合恢复555体</t>
+  </si>
+  <si>
+    <t>战斗结束恢复20%的体</t>
+  </si>
+  <si>
+    <t>战斗结束恢复25%的体</t>
+  </si>
+  <si>
+    <t>战斗结束恢复30%的体</t>
+  </si>
+  <si>
+    <t>战斗结束恢复35%的体</t>
+  </si>
+  <si>
+    <t>战斗结束恢复40%的体</t>
+  </si>
+  <si>
+    <t>飞鹰爪</t>
+  </si>
+  <si>
+    <t>武杀式命中时造成伤口状态</t>
+  </si>
+  <si>
+    <t>赤鼙鼓</t>
+  </si>
+  <si>
+    <t>速,15</t>
+  </si>
+  <si>
+    <t>赤鼙鼓+1</t>
+  </si>
+  <si>
+    <t>速,23</t>
+  </si>
+  <si>
+    <t>赤鼙鼓+2</t>
+  </si>
+  <si>
+    <t>速,34</t>
+  </si>
+  <si>
+    <t>赤鼙鼓+3</t>
+  </si>
+  <si>
+    <t>速,50</t>
+  </si>
+  <si>
+    <t>赤鼙鼓+4</t>
+  </si>
+  <si>
+    <t>速,80</t>
+  </si>
+  <si>
+    <t>红玉坠</t>
+  </si>
+  <si>
+    <t>战斗开始获得2层看破，回合开始获得1层看破</t>
+  </si>
+  <si>
+    <t>红玉坠+1</t>
+  </si>
+  <si>
+    <t>速,2</t>
+  </si>
+  <si>
+    <t>红玉坠+2</t>
+  </si>
+  <si>
+    <t>速,4</t>
+  </si>
+  <si>
+    <t>红玉坠+3</t>
+  </si>
+  <si>
+    <t>速,6</t>
+  </si>
+  <si>
+    <t>红玉坠+4</t>
+  </si>
+  <si>
+    <t>速,8</t>
+  </si>
+  <si>
+    <t>红玉坠+5</t>
+  </si>
+  <si>
+    <t>速,11</t>
+  </si>
+  <si>
+    <t>红玉坠+6</t>
+  </si>
+  <si>
+    <t>速,14</t>
+  </si>
+  <si>
+    <t>红玉坠+7</t>
+  </si>
+  <si>
+    <t>速,17</t>
+  </si>
+  <si>
+    <t>红玉坠+8</t>
+  </si>
+  <si>
+    <t>速,20</t>
+  </si>
+  <si>
+    <t>袖里千机</t>
+  </si>
+  <si>
+    <t>使用招式：掷物时，力的值以400替代，该效果该效果每2个回合可触发一次。</t>
+  </si>
+  <si>
+    <t>袖里千机+1</t>
+  </si>
+  <si>
+    <t>袖里千机+2</t>
+  </si>
+  <si>
+    <t>使用招式：掷物时，力的值以680替代，该效果该效果每2个回合可触发一次。</t>
+  </si>
+  <si>
+    <t>袖里千机+3</t>
+  </si>
+  <si>
+    <t>使用招式：掷物时，力的值以960替代，该效果该效果每2个回合可触发一次。</t>
+  </si>
+  <si>
+    <t>袖里千机+4</t>
+  </si>
+  <si>
+    <t>使用招式：掷物时，力的值以1240替代，该效果该效果每2个回合可触发一次。</t>
+  </si>
+  <si>
+    <t>袖里千机+5</t>
+  </si>
+  <si>
+    <t>使用招式：掷物时，力的值以1660替代，该效果该效果每2个回合可触发一次。</t>
+  </si>
+  <si>
+    <t>袖里千机+6</t>
+  </si>
+  <si>
+    <t>使用招式：掷物时，力的值以2080替代，该效果该效果每2个回合可触发一次。</t>
+  </si>
+  <si>
+    <t>袖里千机+7</t>
+  </si>
+  <si>
+    <t>使用招式：掷物时，力的值以2840替代，该效果该效果每2个回合可触发一次。</t>
+  </si>
+  <si>
+    <t>袖里千机+8</t>
+  </si>
+  <si>
+    <t>使用招式：掷物时，力的值以3600替代，该效果该效果每2个回合可触发一次。</t>
+  </si>
+  <si>
+    <t>巧,15</t>
+  </si>
+  <si>
+    <t>巧,23</t>
+  </si>
+  <si>
+    <t>巧,34</t>
+  </si>
+  <si>
+    <t>巧,50</t>
+  </si>
+  <si>
+    <t>巧,80</t>
+  </si>
+  <si>
+    <t>破,5</t>
+  </si>
+  <si>
+    <t>受到直接攻击后随机获得一种药力状态</t>
+  </si>
+  <si>
+    <t>破,8</t>
+  </si>
+  <si>
+    <t>破,11</t>
+  </si>
+  <si>
+    <t>破,15.5</t>
+  </si>
+  <si>
+    <t>破,27</t>
+  </si>
+  <si>
+    <t>破,34</t>
+  </si>
+  <si>
+    <t>破,46</t>
+  </si>
+  <si>
+    <t>破,58</t>
+  </si>
+  <si>
+    <t>抵免1次致命伤害</t>
+  </si>
+  <si>
+    <t>回合开始获得苦印状态，行动决定后对行动目标施加苦印状态</t>
+  </si>
+  <si>
+    <t>体,79</t>
+  </si>
+  <si>
+    <t>体,158</t>
+  </si>
+  <si>
+    <t>体,240</t>
+  </si>
+  <si>
+    <t>体,323</t>
+  </si>
+  <si>
+    <t>体,443</t>
+  </si>
+  <si>
+    <t>体,563</t>
+  </si>
+  <si>
+    <t>体,789</t>
+  </si>
+  <si>
+    <t>体,1015</t>
+  </si>
+  <si>
+    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成21伤害</t>
+  </si>
+  <si>
+    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成47伤害</t>
+  </si>
+  <si>
+    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成73伤害</t>
+  </si>
+  <si>
+    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成110伤害</t>
+  </si>
+  <si>
+    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成148伤害</t>
+  </si>
+  <si>
+    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成190伤害</t>
+  </si>
+  <si>
+    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成243伤害</t>
+  </si>
+  <si>
+    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成339伤害</t>
+  </si>
+  <si>
+    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成434伤害</t>
+  </si>
+  <si>
+    <t>精古开山刀</t>
+  </si>
+  <si>
+    <t>武杀式命中后扣除目标240+GR*3体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
+  </si>
+  <si>
+    <t>精古开山刀+1</t>
+  </si>
+  <si>
+    <t>武杀式命中后扣除目标240+GR*5体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
+  </si>
+  <si>
+    <t>精古开山刀+2</t>
+  </si>
+  <si>
+    <t>武杀式命中后扣除目标280+GR*5体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
+  </si>
+  <si>
+    <t>精古开山刀+3</t>
+  </si>
+  <si>
+    <t>武杀式命中后扣除目标280+GR*7体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
+  </si>
+  <si>
+    <t>精古开山刀+4</t>
+  </si>
+  <si>
+    <t>武杀式命中后扣除目标340+GR*7体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
+  </si>
+  <si>
+    <t>精古开山刀+5</t>
+  </si>
+  <si>
+    <t>精古开山刀+6</t>
+  </si>
+  <si>
+    <t>武杀式命中后扣除目标880+GR*9体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
+  </si>
+  <si>
+    <t>精古开山刀+7</t>
+  </si>
+  <si>
+    <t>武杀式命中后扣除目标880+GR*11体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
+  </si>
+  <si>
+    <t>精古开山刀+8</t>
+  </si>
+  <si>
+    <t>武杀式命中后扣除目标1122+GR*11体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
+  </si>
+  <si>
+    <t>姗岚幡</t>
+  </si>
+  <si>
+    <t>回合开始键的数量为10则获得1层回避状态</t>
+  </si>
+  <si>
+    <t>杀式造成的伤害增加，量为体的1.5%*招式威力</t>
+  </si>
+  <si>
+    <t>在排列行动的先后时，键的数量计算默认为8</t>
+  </si>
+  <si>
+    <t>渡梦舟+1</t>
+  </si>
+  <si>
+    <t>渡梦舟+2</t>
+  </si>
+  <si>
+    <t>渡梦舟+3</t>
+  </si>
+  <si>
+    <t>渡梦舟+4</t>
+  </si>
+  <si>
+    <t>渡梦舟+5</t>
+  </si>
+  <si>
+    <t>渡梦舟+6</t>
+  </si>
+  <si>
+    <t>渡梦舟+7</t>
+  </si>
+  <si>
+    <t>渡梦舟+8</t>
+  </si>
+  <si>
+    <t>拂容绫</t>
+  </si>
+  <si>
+    <t>技,6</t>
+  </si>
+  <si>
+    <t>战斗中角色至多持有3个异常状态</t>
+  </si>
+  <si>
+    <t>拂容绫+1</t>
+  </si>
+  <si>
+    <t>技,10</t>
+  </si>
+  <si>
+    <t>拂容绫+2</t>
+  </si>
+  <si>
+    <t>技,14</t>
+  </si>
+  <si>
+    <t>拂容绫+3</t>
+  </si>
+  <si>
+    <t>技,19.5</t>
+  </si>
+  <si>
+    <t>拂容绫+4</t>
+  </si>
+  <si>
+    <t>拂容绫+5</t>
+  </si>
+  <si>
+    <t>技,33.5</t>
+  </si>
+  <si>
+    <t>拂容绫+6</t>
+  </si>
+  <si>
+    <t>技,44.5</t>
+  </si>
+  <si>
+    <t>拂容绫+7</t>
+  </si>
+  <si>
+    <t>技,57.5</t>
+  </si>
+  <si>
+    <t>拂容绫+8</t>
+  </si>
+  <si>
+    <t>技,72.5</t>
+  </si>
+  <si>
+    <t>行动后目标在本回合对你的直接伤害减少20%</t>
+  </si>
+  <si>
+    <t>瘴珠</t>
+  </si>
+  <si>
+    <t>行动后获得一层毒瘴状态</t>
+  </si>
+  <si>
+    <t>绝世宝剑</t>
+  </si>
+  <si>
+    <t>对木桩造成的伤害提升999%</t>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Property</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ParamList</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=,),float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>额外参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Script</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>脚本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasureBase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.15,0.05,0.05,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.2,0.05,0.05,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.25,0.05,0.05,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.3,0.05,0.05,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.35,0.05,0.05,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.4,0.05,0.05,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.45,0.05,0.05,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5,0.05,0.05,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.55,0.05,0.05,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10070</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>38,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>57,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>68,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>84,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>130,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>160,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10079</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始随机消耗键直至不超过6个，每消耗一个键随机获得1层武增/术增/力增/技增</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,200011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10089</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10117</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10117</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>95</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>140</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>185</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>315</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>435</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>555</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10126</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10126</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10137</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10137</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10138</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10178</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10178</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10205</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10205</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10224</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10224</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10242</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10242</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10107</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用招式：掷物时，力的值以590替代，该效果该效果每2个回合可触发一次。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武杀式命中后扣除目标340+GR*9体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击精兽时倍率增加5百分比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杀式造成的伤害增加，量为体的1.5%*招式威力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05,0.15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05,0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05,0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05,0.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05,0.75</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05,0.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05,1.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05,1.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>125,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>125,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>132,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>132,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>158,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>158,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>510,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Feature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10098</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10098</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10131</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10168</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10169</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10169</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10187</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10187</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,500,5,21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,500,5,47</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,500,5,73</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,500,5,110</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,500,5,148</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,500,5,190</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,500,5,243</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,500,5,339</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,500,5,434</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10196</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10196</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240,3,3,0.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240,5,3,0.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>280,5,3,0.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>280,7,3,0.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>340,7,3,0.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>340,9,3,0.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>880,9,3,0.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>880,11,3,0.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1122,11,3,0.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10206</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10206</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>渡梦舟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10233</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10233</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10160</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10160</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10112</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10112</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -79,7 +1704,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,13 +1727,33 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -125,12 +1770,36 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -446,13 +2115,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:M246"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9" style="1"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="4" width="12.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="18.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="89.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="81" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -460,61 +2137,5752 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="33" x14ac:dyDescent="0.2">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3">
+        <v>10001</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="J4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" spans="1:13" ht="33" x14ac:dyDescent="0.2">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3">
+        <v>10002</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="D5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+    </row>
+    <row r="6" spans="1:13" ht="33" x14ac:dyDescent="0.2">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3">
+        <v>10003</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="3"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" spans="1:13" ht="33" x14ac:dyDescent="0.2">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3">
+        <v>10004</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" ht="33" x14ac:dyDescent="0.2">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3">
+        <v>10005</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="3"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+    </row>
+    <row r="9" spans="1:13" ht="33" x14ac:dyDescent="0.2">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3">
+        <v>10006</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="3"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" spans="1:13" ht="33" x14ac:dyDescent="0.2">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3">
+        <v>10007</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="3"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+    </row>
+    <row r="11" spans="1:13" ht="33" x14ac:dyDescent="0.2">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3">
+        <v>10008</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J11" s="3"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+    </row>
+    <row r="12" spans="1:13" ht="33" x14ac:dyDescent="0.2">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3">
+        <v>10009</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="3"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+    </row>
+    <row r="13" spans="1:13" ht="33" x14ac:dyDescent="0.2">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3">
+        <v>10010</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" s="3"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3">
+        <v>10011</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="J14" s="3"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3">
+        <v>10012</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" s="3"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3">
+        <v>10013</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J16" s="3"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3">
+        <v>10014</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J17" s="3"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3">
+        <v>10015</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3">
+        <v>10016</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J19" s="3"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3">
+        <v>10017</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J20" s="3"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3">
+        <v>10018</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J21" s="3"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3">
+        <v>10019</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+    </row>
+    <row r="23" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6">
+        <v>10020</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6">
+        <v>10021</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6">
+        <v>10022</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6">
+        <v>10023</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6">
+        <v>10024</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3">
+        <v>10025</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J28" s="3"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3">
+        <v>10026</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J29" s="3"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3">
+        <v>10027</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J30" s="3"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3">
+        <v>10028</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J31" s="3"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3">
+        <v>10029</v>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J32" s="3"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3">
+        <v>10030</v>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J33" s="3"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3">
+        <v>10031</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J34" s="3"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3">
+        <v>10032</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J35" s="3"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3">
+        <v>10033</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J36" s="3"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+    </row>
+    <row r="37" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="6"/>
+      <c r="B37" s="6">
+        <v>10034</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+    </row>
+    <row r="38" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6">
+        <v>10035</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3">
+        <v>10036</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="F39" s="3"/>
+      <c r="G39" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J39" s="3"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3">
+        <v>10037</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="F40" s="3"/>
+      <c r="G40" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J40" s="3"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3">
+        <v>10038</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J41" s="3"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3">
+        <v>10039</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J42" s="3"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3">
+        <v>10040</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J43" s="3"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3">
+        <v>10041</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J44" s="3"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3">
+        <v>10042</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J45" s="3"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3">
+        <v>10043</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J46" s="3"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3">
+        <v>10044</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="F47" s="3"/>
+      <c r="G47" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J47" s="3"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+    </row>
+    <row r="48" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="6"/>
+      <c r="B48" s="6">
+        <v>10045</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D48" s="6"/>
+      <c r="F48" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
+      <c r="M48" s="9"/>
+    </row>
+    <row r="49" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="6"/>
+      <c r="B49" s="6">
+        <v>10046</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D49" s="6"/>
+      <c r="F49" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="9"/>
+      <c r="M49" s="9"/>
+    </row>
+    <row r="50" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="6"/>
+      <c r="B50" s="6">
+        <v>10047</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D50" s="6"/>
+      <c r="F50" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="9"/>
+      <c r="L50" s="9"/>
+      <c r="M50" s="9"/>
+    </row>
+    <row r="51" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="6"/>
+      <c r="B51" s="6">
+        <v>10048</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D51" s="6"/>
+      <c r="F51" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="9"/>
+      <c r="M51" s="9"/>
+    </row>
+    <row r="52" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="6"/>
+      <c r="B52" s="6">
+        <v>10049</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D52" s="6"/>
+      <c r="F52" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="9"/>
+      <c r="L52" s="9"/>
+      <c r="M52" s="9"/>
+    </row>
+    <row r="53" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="6"/>
+      <c r="B53" s="6">
+        <v>10050</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D53" s="6"/>
+      <c r="F53" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="9"/>
+      <c r="L53" s="9"/>
+      <c r="M53" s="9"/>
+    </row>
+    <row r="54" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="6"/>
+      <c r="B54" s="6">
+        <v>10051</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D54" s="6"/>
+      <c r="F54" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="9"/>
+      <c r="L54" s="9"/>
+      <c r="M54" s="9"/>
+    </row>
+    <row r="55" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="6"/>
+      <c r="B55" s="6">
+        <v>10052</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D55" s="6"/>
+      <c r="F55" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="9"/>
+      <c r="L55" s="9"/>
+      <c r="M55" s="9"/>
+    </row>
+    <row r="56" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="6"/>
+      <c r="B56" s="6">
+        <v>10053</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D56" s="6"/>
+      <c r="F56" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="9"/>
+      <c r="L56" s="9"/>
+      <c r="M56" s="9"/>
+    </row>
+    <row r="57" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="6"/>
+      <c r="B57" s="6">
+        <v>10054</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D57" s="6"/>
+      <c r="F57" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="9"/>
+      <c r="L57" s="9"/>
+      <c r="M57" s="9"/>
+    </row>
+    <row r="58" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="6"/>
+      <c r="B58" s="6">
+        <v>10055</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D58" s="6"/>
+      <c r="F58" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="9"/>
+      <c r="L58" s="9"/>
+      <c r="M58" s="9"/>
+    </row>
+    <row r="59" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="6"/>
+      <c r="B59" s="6">
+        <v>10056</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D59" s="6"/>
+      <c r="F59" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="9"/>
+      <c r="L59" s="9"/>
+      <c r="M59" s="9"/>
+    </row>
+    <row r="60" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="6"/>
+      <c r="B60" s="6">
+        <v>10057</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D60" s="6"/>
+      <c r="F60" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="9"/>
+      <c r="L60" s="9"/>
+      <c r="M60" s="9"/>
+    </row>
+    <row r="61" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="6"/>
+      <c r="B61" s="6">
+        <v>10058</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D61" s="6"/>
+      <c r="F61" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="9"/>
+      <c r="L61" s="9"/>
+      <c r="M61" s="9"/>
+    </row>
+    <row r="62" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="6"/>
+      <c r="B62" s="6">
+        <v>10059</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D62" s="6"/>
+      <c r="F62" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="9"/>
+      <c r="L62" s="9"/>
+      <c r="M62" s="9"/>
+    </row>
+    <row r="63" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="6"/>
+      <c r="B63" s="6">
+        <v>10060</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D63" s="6"/>
+      <c r="F63" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="9"/>
+      <c r="L63" s="9"/>
+      <c r="M63" s="9"/>
+    </row>
+    <row r="64" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="6"/>
+      <c r="B64" s="6">
+        <v>10061</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D64" s="6"/>
+      <c r="F64" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="9"/>
+      <c r="L64" s="9"/>
+      <c r="M64" s="9"/>
+    </row>
+    <row r="65" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="6"/>
+      <c r="B65" s="6">
+        <v>10062</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D65" s="6"/>
+      <c r="F65" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H65" s="6"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="9"/>
+      <c r="L65" s="9"/>
+      <c r="M65" s="9"/>
+    </row>
+    <row r="66" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="6"/>
+      <c r="B66" s="6">
+        <v>10063</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D66" s="6"/>
+      <c r="F66" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="9"/>
+      <c r="L66" s="9"/>
+      <c r="M66" s="9"/>
+    </row>
+    <row r="67" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="6"/>
+      <c r="B67" s="6">
+        <v>10064</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D67" s="6"/>
+      <c r="F67" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="9"/>
+      <c r="L67" s="9"/>
+      <c r="M67" s="9"/>
+    </row>
+    <row r="68" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="6"/>
+      <c r="B68" s="6">
+        <v>10065</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D68" s="6"/>
+      <c r="F68" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H68" s="6"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="6"/>
+      <c r="K68" s="9"/>
+      <c r="L68" s="9"/>
+      <c r="M68" s="9"/>
+    </row>
+    <row r="69" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="6"/>
+      <c r="B69" s="6">
+        <v>10066</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D69" s="6"/>
+      <c r="F69" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="9"/>
+      <c r="L69" s="9"/>
+      <c r="M69" s="9"/>
+    </row>
+    <row r="70" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="6"/>
+      <c r="B70" s="6">
+        <v>10067</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D70" s="6"/>
+      <c r="F70" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H70" s="6"/>
+      <c r="I70" s="6"/>
+      <c r="J70" s="6"/>
+      <c r="K70" s="9"/>
+      <c r="L70" s="9"/>
+      <c r="M70" s="9"/>
+    </row>
+    <row r="71" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="6"/>
+      <c r="B71" s="6">
+        <v>10068</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D71" s="6"/>
+      <c r="F71" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H71" s="6"/>
+      <c r="I71" s="6"/>
+      <c r="J71" s="6"/>
+      <c r="K71" s="9"/>
+      <c r="L71" s="9"/>
+      <c r="M71" s="9"/>
+    </row>
+    <row r="72" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="6"/>
+      <c r="B72" s="6">
+        <v>10069</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D72" s="6"/>
+      <c r="F72" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6"/>
+      <c r="J72" s="6"/>
+      <c r="K72" s="9"/>
+      <c r="L72" s="9"/>
+      <c r="M72" s="9"/>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A73" s="3"/>
+      <c r="B73" s="3">
+        <v>10070</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J73" s="3"/>
+      <c r="K73" s="2"/>
+      <c r="L73" s="2"/>
+      <c r="M73" s="2"/>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A74" s="3"/>
+      <c r="B74" s="3">
+        <v>10071</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D74" s="3"/>
+      <c r="F74" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J74" s="3"/>
+      <c r="K74" s="2"/>
+      <c r="L74" s="2"/>
+      <c r="M74" s="2"/>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3">
+        <v>10072</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D75" s="3"/>
+      <c r="F75" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J75" s="3"/>
+      <c r="K75" s="2"/>
+      <c r="L75" s="2"/>
+      <c r="M75" s="2"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3">
+        <v>10073</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D76" s="3"/>
+      <c r="F76" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J76" s="3"/>
+      <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
+      <c r="M76" s="2"/>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3">
+        <v>10074</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D77" s="3"/>
+      <c r="F77" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="J77" s="3"/>
+      <c r="K77" s="2"/>
+      <c r="L77" s="2"/>
+      <c r="M77" s="2"/>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3">
+        <v>10075</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D78" s="3"/>
+      <c r="F78" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J78" s="3"/>
+      <c r="K78" s="2"/>
+      <c r="L78" s="2"/>
+      <c r="M78" s="2"/>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A79" s="3"/>
+      <c r="B79" s="3">
+        <v>10076</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D79" s="3"/>
+      <c r="F79" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J79" s="3"/>
+      <c r="K79" s="2"/>
+      <c r="L79" s="2"/>
+      <c r="M79" s="2"/>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3">
+        <v>10077</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D80" s="3"/>
+      <c r="F80" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="J80" s="3"/>
+      <c r="K80" s="2"/>
+      <c r="L80" s="2"/>
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A81" s="3"/>
+      <c r="B81" s="3">
+        <v>10078</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D81" s="3"/>
+      <c r="F81" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J81" s="3"/>
+      <c r="K81" s="2"/>
+      <c r="L81" s="2"/>
+      <c r="M81" s="2"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A82" s="3"/>
+      <c r="B82" s="3">
+        <v>10079</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D82" s="3"/>
+      <c r="F82" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="J82" s="3"/>
+      <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
+      <c r="M82" s="2"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A83" s="3"/>
+      <c r="B83" s="3">
+        <v>10080</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D83" s="3"/>
+      <c r="F83" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J83" s="3"/>
+      <c r="K83" s="2"/>
+      <c r="L83" s="2"/>
+      <c r="M83" s="2"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3">
+        <v>10081</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D84" s="3"/>
+      <c r="F84" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J84" s="3"/>
+      <c r="K84" s="2"/>
+      <c r="L84" s="2"/>
+      <c r="M84" s="2"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A85" s="3"/>
+      <c r="B85" s="3">
+        <v>10082</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D85" s="3"/>
+      <c r="F85" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J85" s="3"/>
+      <c r="K85" s="2"/>
+      <c r="L85" s="2"/>
+      <c r="M85" s="2"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A86" s="3"/>
+      <c r="B86" s="3">
+        <v>10083</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D86" s="3"/>
+      <c r="F86" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J86" s="3"/>
+      <c r="K86" s="2"/>
+      <c r="L86" s="2"/>
+      <c r="M86" s="2"/>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A87" s="3"/>
+      <c r="B87" s="3">
+        <v>10084</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D87" s="3"/>
+      <c r="F87" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J87" s="3"/>
+      <c r="K87" s="2"/>
+      <c r="L87" s="2"/>
+      <c r="M87" s="2"/>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A88" s="3"/>
+      <c r="B88" s="3">
+        <v>10085</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D88" s="3"/>
+      <c r="F88" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J88" s="3"/>
+      <c r="K88" s="2"/>
+      <c r="L88" s="2"/>
+      <c r="M88" s="2"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A89" s="3"/>
+      <c r="B89" s="3">
+        <v>10086</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D89" s="3"/>
+      <c r="F89" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J89" s="3"/>
+      <c r="K89" s="2"/>
+      <c r="L89" s="2"/>
+      <c r="M89" s="2"/>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A90" s="3"/>
+      <c r="B90" s="3">
+        <v>10087</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D90" s="3"/>
+      <c r="F90" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J90" s="3"/>
+      <c r="K90" s="2"/>
+      <c r="L90" s="2"/>
+      <c r="M90" s="2"/>
+    </row>
+    <row r="91" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="6"/>
+      <c r="B91" s="6">
+        <v>10088</v>
+      </c>
+      <c r="C91" s="6"/>
+      <c r="D91" s="6"/>
+      <c r="F91" s="6"/>
+      <c r="G91" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H91" s="6"/>
+      <c r="I91" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="J91" s="6"/>
+      <c r="K91" s="9"/>
+      <c r="L91" s="9"/>
+      <c r="M91" s="9"/>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A92" s="3"/>
+      <c r="B92" s="3">
+        <v>10089</v>
+      </c>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="F92" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J92" s="3"/>
+      <c r="K92" s="2"/>
+      <c r="L92" s="2"/>
+      <c r="M92" s="2"/>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A93" s="3"/>
+      <c r="B93" s="3">
+        <v>10090</v>
+      </c>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="F93" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J93" s="3"/>
+      <c r="K93" s="2"/>
+      <c r="L93" s="2"/>
+      <c r="M93" s="2"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A94" s="3"/>
+      <c r="B94" s="3">
+        <v>10091</v>
+      </c>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="F94" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J94" s="3"/>
+      <c r="K94" s="2"/>
+      <c r="L94" s="2"/>
+      <c r="M94" s="2"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A95" s="3"/>
+      <c r="B95" s="3">
+        <v>10092</v>
+      </c>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="F95" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J95" s="3"/>
+      <c r="K95" s="2"/>
+      <c r="L95" s="2"/>
+      <c r="M95" s="2"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A96" s="3"/>
+      <c r="B96" s="3">
+        <v>10093</v>
+      </c>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="F96" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J96" s="3"/>
+      <c r="K96" s="2"/>
+      <c r="L96" s="2"/>
+      <c r="M96" s="2"/>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A97" s="3"/>
+      <c r="B97" s="3">
+        <v>10094</v>
+      </c>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="F97" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J97" s="3"/>
+      <c r="K97" s="2"/>
+      <c r="L97" s="2"/>
+      <c r="M97" s="2"/>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A98" s="3"/>
+      <c r="B98" s="3">
+        <v>10095</v>
+      </c>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="F98" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J98" s="3"/>
+      <c r="K98" s="2"/>
+      <c r="L98" s="2"/>
+      <c r="M98" s="2"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A99" s="3"/>
+      <c r="B99" s="3">
+        <v>10096</v>
+      </c>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="F99" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J99" s="3"/>
+      <c r="K99" s="2"/>
+      <c r="L99" s="2"/>
+      <c r="M99" s="2"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A100" s="3"/>
+      <c r="B100" s="3">
+        <v>10097</v>
+      </c>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="F100" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J100" s="3"/>
+      <c r="K100" s="2"/>
+      <c r="L100" s="2"/>
+      <c r="M100" s="2"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A101" s="3"/>
+      <c r="B101" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D101" s="3"/>
+      <c r="F101" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="H101" s="3"/>
+      <c r="I101" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J101" s="3"/>
+      <c r="K101" s="2"/>
+      <c r="L101" s="2"/>
+      <c r="M101" s="2"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A102" s="3"/>
+      <c r="B102" s="3">
+        <v>10099</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D102" s="3"/>
+      <c r="F102" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="H102" s="3"/>
+      <c r="I102" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J102" s="3"/>
+      <c r="K102" s="2"/>
+      <c r="L102" s="2"/>
+      <c r="M102" s="2"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A103" s="3"/>
+      <c r="B103" s="3">
+        <v>10100</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D103" s="3"/>
+      <c r="F103" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="H103" s="3"/>
+      <c r="I103" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J103" s="3"/>
+      <c r="K103" s="2"/>
+      <c r="L103" s="2"/>
+      <c r="M103" s="2"/>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A104" s="3"/>
+      <c r="B104" s="3">
+        <v>10101</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D104" s="3"/>
+      <c r="F104" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="H104" s="3"/>
+      <c r="I104" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J104" s="3"/>
+      <c r="K104" s="2"/>
+      <c r="L104" s="2"/>
+      <c r="M104" s="2"/>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A105" s="3"/>
+      <c r="B105" s="3">
+        <v>10102</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D105" s="3"/>
+      <c r="F105" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="H105" s="3"/>
+      <c r="I105" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J105" s="3"/>
+      <c r="K105" s="2"/>
+      <c r="L105" s="2"/>
+      <c r="M105" s="2"/>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A106" s="3"/>
+      <c r="B106" s="3">
+        <v>10103</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D106" s="3"/>
+      <c r="F106" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="H106" s="3"/>
+      <c r="I106" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J106" s="3"/>
+      <c r="K106" s="2"/>
+      <c r="L106" s="2"/>
+      <c r="M106" s="2"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A107" s="3"/>
+      <c r="B107" s="3">
+        <v>10104</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D107" s="3"/>
+      <c r="F107" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="H107" s="3"/>
+      <c r="I107" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J107" s="3"/>
+      <c r="K107" s="2"/>
+      <c r="L107" s="2"/>
+      <c r="M107" s="2"/>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A108" s="3"/>
+      <c r="B108" s="3">
+        <v>10105</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D108" s="3"/>
+      <c r="F108" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="H108" s="3"/>
+      <c r="I108" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J108" s="3"/>
+      <c r="K108" s="2"/>
+      <c r="L108" s="2"/>
+      <c r="M108" s="2"/>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A109" s="3"/>
+      <c r="B109" s="3">
+        <v>10106</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D109" s="3"/>
+      <c r="F109" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="H109" s="3"/>
+      <c r="I109" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J109" s="3"/>
+      <c r="K109" s="2"/>
+      <c r="L109" s="2"/>
+      <c r="M109" s="2"/>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A110" s="3"/>
+      <c r="B110" s="3">
+        <v>10107</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D110" s="3"/>
+      <c r="F110" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J110" s="3"/>
+      <c r="K110" s="2"/>
+      <c r="L110" s="2"/>
+      <c r="M110" s="2"/>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A111" s="3"/>
+      <c r="B111" s="3">
+        <v>10108</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D111" s="3"/>
+      <c r="F111" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J111" s="3"/>
+      <c r="K111" s="2"/>
+      <c r="L111" s="2"/>
+      <c r="M111" s="2"/>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A112" s="3"/>
+      <c r="B112" s="3">
+        <v>10109</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D112" s="3"/>
+      <c r="F112" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="J112" s="3"/>
+      <c r="K112" s="2"/>
+      <c r="L112" s="2"/>
+      <c r="M112" s="2"/>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A113" s="3"/>
+      <c r="B113" s="3">
+        <v>10110</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D113" s="3"/>
+      <c r="F113" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="J113" s="3"/>
+      <c r="K113" s="2"/>
+      <c r="L113" s="2"/>
+      <c r="M113" s="2"/>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A114" s="3"/>
+      <c r="B114" s="3">
+        <v>10111</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D114" s="3"/>
+      <c r="F114" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="J114" s="3"/>
+      <c r="K114" s="2"/>
+      <c r="L114" s="2"/>
+      <c r="M114" s="2"/>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A115" s="3"/>
+      <c r="B115" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="J115" s="3"/>
+      <c r="K115" s="2"/>
+      <c r="L115" s="2"/>
+      <c r="M115" s="2"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A116" s="3"/>
+      <c r="B116" s="3">
+        <v>10113</v>
+      </c>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="J116" s="3"/>
+      <c r="K116" s="2"/>
+      <c r="L116" s="2"/>
+      <c r="M116" s="2"/>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A117" s="3"/>
+      <c r="B117" s="3">
+        <v>10114</v>
+      </c>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="J117" s="3"/>
+      <c r="K117" s="2"/>
+      <c r="L117" s="2"/>
+      <c r="M117" s="2"/>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A118" s="3"/>
+      <c r="B118" s="3">
+        <v>10115</v>
+      </c>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="J118" s="3"/>
+      <c r="K118" s="2"/>
+      <c r="L118" s="2"/>
+      <c r="M118" s="2"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A119" s="3"/>
+      <c r="B119" s="3">
+        <v>10116</v>
+      </c>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="J119" s="3"/>
+      <c r="K119" s="2"/>
+      <c r="L119" s="2"/>
+      <c r="M119" s="2"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A120" s="3"/>
+      <c r="B120" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="F120" s="3"/>
+      <c r="G120" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="J120" s="3"/>
+      <c r="K120" s="2"/>
+      <c r="L120" s="2"/>
+      <c r="M120" s="2"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A121" s="3"/>
+      <c r="B121" s="3">
+        <v>10118</v>
+      </c>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="F121" s="3"/>
+      <c r="G121" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="J121" s="3"/>
+      <c r="K121" s="2"/>
+      <c r="L121" s="2"/>
+      <c r="M121" s="2"/>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A122" s="3"/>
+      <c r="B122" s="3">
+        <v>10119</v>
+      </c>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="F122" s="3"/>
+      <c r="G122" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="J122" s="3"/>
+      <c r="K122" s="2"/>
+      <c r="L122" s="2"/>
+      <c r="M122" s="2"/>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A123" s="3"/>
+      <c r="B123" s="3">
+        <v>10120</v>
+      </c>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="F123" s="3"/>
+      <c r="G123" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="J123" s="3"/>
+      <c r="K123" s="2"/>
+      <c r="L123" s="2"/>
+      <c r="M123" s="2"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A124" s="3"/>
+      <c r="B124" s="3">
+        <v>10121</v>
+      </c>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="F124" s="3"/>
+      <c r="G124" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="J124" s="3"/>
+      <c r="K124" s="2"/>
+      <c r="L124" s="2"/>
+      <c r="M124" s="2"/>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A125" s="3"/>
+      <c r="B125" s="3">
+        <v>10122</v>
+      </c>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
+      <c r="F125" s="3"/>
+      <c r="G125" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="J125" s="3"/>
+      <c r="K125" s="2"/>
+      <c r="L125" s="2"/>
+      <c r="M125" s="2"/>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A126" s="3"/>
+      <c r="B126" s="3">
+        <v>10123</v>
+      </c>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="F126" s="3"/>
+      <c r="G126" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="J126" s="3"/>
+      <c r="K126" s="2"/>
+      <c r="L126" s="2"/>
+      <c r="M126" s="2"/>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A127" s="3"/>
+      <c r="B127" s="3">
+        <v>10124</v>
+      </c>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
+      <c r="F127" s="3"/>
+      <c r="G127" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="I127" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="J127" s="3"/>
+      <c r="K127" s="2"/>
+      <c r="L127" s="2"/>
+      <c r="M127" s="2"/>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A128" s="3"/>
+      <c r="B128" s="3">
+        <v>10125</v>
+      </c>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="F128" s="3"/>
+      <c r="G128" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="J128" s="3"/>
+      <c r="K128" s="2"/>
+      <c r="L128" s="2"/>
+      <c r="M128" s="2"/>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A129" s="3"/>
+      <c r="B129" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+      <c r="F129" s="3"/>
+      <c r="G129" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="H129" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I129" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="J129" s="3"/>
+      <c r="K129" s="2"/>
+      <c r="L129" s="2"/>
+      <c r="M129" s="2"/>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A130" s="3"/>
+      <c r="B130" s="3">
+        <v>10127</v>
+      </c>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="F130" s="3"/>
+      <c r="G130" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="H130" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="I130" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="J130" s="3"/>
+      <c r="K130" s="2"/>
+      <c r="L130" s="2"/>
+      <c r="M130" s="2"/>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A131" s="3"/>
+      <c r="B131" s="3">
+        <v>10128</v>
+      </c>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="F131" s="3"/>
+      <c r="G131" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="I131" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="J131" s="3"/>
+      <c r="K131" s="2"/>
+      <c r="L131" s="2"/>
+      <c r="M131" s="2"/>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A132" s="3"/>
+      <c r="B132" s="3">
+        <v>10129</v>
+      </c>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="F132" s="3"/>
+      <c r="G132" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="H132" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="I132" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="J132" s="3"/>
+      <c r="K132" s="2"/>
+      <c r="L132" s="2"/>
+      <c r="M132" s="2"/>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A133" s="3"/>
+      <c r="B133" s="3">
+        <v>10130</v>
+      </c>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="F133" s="3"/>
+      <c r="G133" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="I133" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="J133" s="3"/>
+      <c r="K133" s="2"/>
+      <c r="L133" s="2"/>
+      <c r="M133" s="2"/>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A134" s="3"/>
+      <c r="B134" s="3">
+        <v>10131</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D134" s="3"/>
+      <c r="F134" s="3"/>
+      <c r="G134" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="J134" s="3"/>
+      <c r="K134" s="2"/>
+      <c r="L134" s="2"/>
+      <c r="M134" s="2"/>
+    </row>
+    <row r="135" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="6"/>
+      <c r="B135" s="6">
+        <v>10132</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="D135" s="6"/>
+      <c r="F135" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H135" s="6"/>
+      <c r="I135" s="6"/>
+      <c r="J135" s="6"/>
+      <c r="K135" s="9"/>
+      <c r="L135" s="9"/>
+      <c r="M135" s="9"/>
+    </row>
+    <row r="136" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="6"/>
+      <c r="B136" s="6">
+        <v>10133</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D136" s="6"/>
+      <c r="F136" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="G136" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H136" s="6"/>
+      <c r="I136" s="6"/>
+      <c r="J136" s="6"/>
+      <c r="K136" s="9"/>
+      <c r="L136" s="9"/>
+      <c r="M136" s="9"/>
+    </row>
+    <row r="137" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="6"/>
+      <c r="B137" s="6">
+        <v>10134</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="D137" s="6"/>
+      <c r="F137" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H137" s="6"/>
+      <c r="I137" s="6"/>
+      <c r="J137" s="6"/>
+      <c r="K137" s="9"/>
+      <c r="L137" s="9"/>
+      <c r="M137" s="9"/>
+    </row>
+    <row r="138" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="6"/>
+      <c r="B138" s="6">
+        <v>10135</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D138" s="6"/>
+      <c r="F138" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H138" s="6"/>
+      <c r="I138" s="6"/>
+      <c r="J138" s="6"/>
+      <c r="K138" s="9"/>
+      <c r="L138" s="9"/>
+      <c r="M138" s="9"/>
+    </row>
+    <row r="139" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="6"/>
+      <c r="B139" s="6">
+        <v>10136</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D139" s="6"/>
+      <c r="F139" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="G139" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H139" s="6"/>
+      <c r="I139" s="6"/>
+      <c r="J139" s="6"/>
+      <c r="K139" s="9"/>
+      <c r="L139" s="9"/>
+      <c r="M139" s="9"/>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A140" s="3"/>
+      <c r="B140" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D140" s="3"/>
+      <c r="F140" s="3"/>
+      <c r="G140" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="H140" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J140" s="3"/>
+      <c r="K140" s="2"/>
+      <c r="L140" s="2"/>
+      <c r="M140" s="2"/>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A141" s="3"/>
+      <c r="B141" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D141" s="3"/>
+      <c r="F141" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="H141" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="I141" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J141" s="3"/>
+      <c r="K141" s="2"/>
+      <c r="L141" s="2"/>
+      <c r="M141" s="2"/>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A142" s="3"/>
+      <c r="B142" s="3">
+        <v>10139</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D142" s="3"/>
+      <c r="F142" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="H142" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="I142" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J142" s="3"/>
+      <c r="K142" s="2"/>
+      <c r="L142" s="2"/>
+      <c r="M142" s="2"/>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A143" s="3"/>
+      <c r="B143" s="3">
+        <v>10140</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D143" s="3"/>
+      <c r="F143" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="H143" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="I143" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J143" s="3"/>
+      <c r="K143" s="2"/>
+      <c r="L143" s="2"/>
+      <c r="M143" s="2"/>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A144" s="3"/>
+      <c r="B144" s="3">
+        <v>10141</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D144" s="3"/>
+      <c r="F144" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="H144" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="I144" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J144" s="3"/>
+      <c r="K144" s="2"/>
+      <c r="L144" s="2"/>
+      <c r="M144" s="2"/>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A145" s="3"/>
+      <c r="B145" s="3">
+        <v>10142</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D145" s="3"/>
+      <c r="F145" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="H145" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="I145" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J145" s="3"/>
+      <c r="K145" s="2"/>
+      <c r="L145" s="2"/>
+      <c r="M145" s="2"/>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A146" s="3"/>
+      <c r="B146" s="3">
+        <v>10143</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D146" s="3"/>
+      <c r="F146" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="H146" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J146" s="3"/>
+      <c r="K146" s="2"/>
+      <c r="L146" s="2"/>
+      <c r="M146" s="2"/>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A147" s="3"/>
+      <c r="B147" s="3">
+        <v>10144</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D147" s="3"/>
+      <c r="F147" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="H147" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="I147" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J147" s="3"/>
+      <c r="K147" s="2"/>
+      <c r="L147" s="2"/>
+      <c r="M147" s="2"/>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A148" s="3"/>
+      <c r="B148" s="3">
+        <v>10145</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D148" s="3"/>
+      <c r="F148" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="H148" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="I148" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J148" s="3"/>
+      <c r="K148" s="2"/>
+      <c r="L148" s="2"/>
+      <c r="M148" s="2"/>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A149" s="6"/>
+      <c r="B149" s="6">
+        <v>10146</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D149" s="6"/>
+      <c r="E149" s="7"/>
+      <c r="F149" s="6"/>
+      <c r="G149" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H149" s="6"/>
+      <c r="I149" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="J149" s="3"/>
+      <c r="K149" s="2"/>
+      <c r="L149" s="2"/>
+      <c r="M149" s="2"/>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A150" s="6"/>
+      <c r="B150" s="6">
+        <v>10147</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="D150" s="6"/>
+      <c r="E150" s="7"/>
+      <c r="F150" s="6"/>
+      <c r="G150" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H150" s="6"/>
+      <c r="I150" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="J150" s="3"/>
+      <c r="K150" s="2"/>
+      <c r="L150" s="2"/>
+      <c r="M150" s="2"/>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A151" s="6"/>
+      <c r="B151" s="6">
+        <v>10148</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="D151" s="6"/>
+      <c r="E151" s="7"/>
+      <c r="F151" s="6"/>
+      <c r="G151" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H151" s="6"/>
+      <c r="I151" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="J151" s="3"/>
+      <c r="K151" s="2"/>
+      <c r="L151" s="2"/>
+      <c r="M151" s="2"/>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A152" s="6"/>
+      <c r="B152" s="6">
+        <v>10149</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="D152" s="6"/>
+      <c r="E152" s="7"/>
+      <c r="F152" s="6"/>
+      <c r="G152" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H152" s="6"/>
+      <c r="I152" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="J152" s="3"/>
+      <c r="K152" s="2"/>
+      <c r="L152" s="2"/>
+      <c r="M152" s="2"/>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A153" s="6"/>
+      <c r="B153" s="6">
+        <v>10150</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="D153" s="6"/>
+      <c r="E153" s="7"/>
+      <c r="F153" s="6"/>
+      <c r="G153" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H153" s="6"/>
+      <c r="I153" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="J153" s="3"/>
+      <c r="K153" s="2"/>
+      <c r="L153" s="2"/>
+      <c r="M153" s="2"/>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A154" s="6"/>
+      <c r="B154" s="6">
+        <v>10151</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="D154" s="6"/>
+      <c r="E154" s="7"/>
+      <c r="F154" s="6"/>
+      <c r="G154" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H154" s="6"/>
+      <c r="I154" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="J154" s="3"/>
+      <c r="K154" s="2"/>
+      <c r="L154" s="2"/>
+      <c r="M154" s="2"/>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A155" s="6"/>
+      <c r="B155" s="6">
+        <v>10152</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="D155" s="6"/>
+      <c r="E155" s="7"/>
+      <c r="F155" s="6"/>
+      <c r="G155" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H155" s="6"/>
+      <c r="I155" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="J155" s="3"/>
+      <c r="K155" s="2"/>
+      <c r="L155" s="2"/>
+      <c r="M155" s="2"/>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A156" s="6"/>
+      <c r="B156" s="6">
+        <v>10153</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="D156" s="6"/>
+      <c r="E156" s="7"/>
+      <c r="F156" s="6"/>
+      <c r="G156" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H156" s="6"/>
+      <c r="I156" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="J156" s="3"/>
+      <c r="K156" s="2"/>
+      <c r="L156" s="2"/>
+      <c r="M156" s="2"/>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A157" s="6"/>
+      <c r="B157" s="6">
+        <v>10154</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="D157" s="6"/>
+      <c r="E157" s="7"/>
+      <c r="F157" s="6"/>
+      <c r="G157" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H157" s="6"/>
+      <c r="I157" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="J157" s="3"/>
+      <c r="K157" s="2"/>
+      <c r="L157" s="2"/>
+      <c r="M157" s="2"/>
+    </row>
+    <row r="158" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="6"/>
+      <c r="B158" s="6">
+        <v>10155</v>
+      </c>
+      <c r="C158" s="6"/>
+      <c r="D158" s="6"/>
+      <c r="F158" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H158" s="6"/>
+      <c r="I158" s="6"/>
+      <c r="J158" s="6"/>
+      <c r="K158" s="9"/>
+      <c r="L158" s="9"/>
+      <c r="M158" s="9"/>
+    </row>
+    <row r="159" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="6"/>
+      <c r="B159" s="6">
+        <v>10156</v>
+      </c>
+      <c r="C159" s="6"/>
+      <c r="D159" s="6"/>
+      <c r="F159" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="G159" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H159" s="6"/>
+      <c r="I159" s="6"/>
+      <c r="J159" s="6"/>
+      <c r="K159" s="9"/>
+      <c r="L159" s="9"/>
+      <c r="M159" s="9"/>
+    </row>
+    <row r="160" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="6"/>
+      <c r="B160" s="6">
+        <v>10157</v>
+      </c>
+      <c r="C160" s="6"/>
+      <c r="D160" s="6"/>
+      <c r="F160" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G160" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H160" s="6"/>
+      <c r="I160" s="6"/>
+      <c r="J160" s="6"/>
+      <c r="K160" s="9"/>
+      <c r="L160" s="9"/>
+      <c r="M160" s="9"/>
+    </row>
+    <row r="161" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="6"/>
+      <c r="B161" s="6">
+        <v>10158</v>
+      </c>
+      <c r="C161" s="6"/>
+      <c r="D161" s="6"/>
+      <c r="F161" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="G161" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H161" s="6"/>
+      <c r="I161" s="6"/>
+      <c r="J161" s="6"/>
+      <c r="K161" s="9"/>
+      <c r="L161" s="9"/>
+      <c r="M161" s="9"/>
+    </row>
+    <row r="162" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="6"/>
+      <c r="B162" s="6">
+        <v>10159</v>
+      </c>
+      <c r="C162" s="6"/>
+      <c r="D162" s="6"/>
+      <c r="F162" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H162" s="6"/>
+      <c r="I162" s="6"/>
+      <c r="J162" s="6"/>
+      <c r="K162" s="9"/>
+      <c r="L162" s="9"/>
+      <c r="M162" s="9"/>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A163" s="3"/>
+      <c r="B163" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="C163" s="3"/>
+      <c r="D163" s="3"/>
+      <c r="F163" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="H163" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="I163" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J163" s="3"/>
+      <c r="K163" s="2"/>
+      <c r="L163" s="2"/>
+      <c r="M163" s="2"/>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A164" s="3"/>
+      <c r="B164" s="3">
+        <v>10161</v>
+      </c>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
+      <c r="F164" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="H164" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="I164" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J164" s="3"/>
+      <c r="K164" s="2"/>
+      <c r="L164" s="2"/>
+      <c r="M164" s="2"/>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A165" s="3"/>
+      <c r="B165" s="3">
+        <v>10162</v>
+      </c>
+      <c r="C165" s="3"/>
+      <c r="D165" s="3"/>
+      <c r="F165" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="H165" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="I165" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J165" s="3"/>
+      <c r="K165" s="2"/>
+      <c r="L165" s="2"/>
+      <c r="M165" s="2"/>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A166" s="3"/>
+      <c r="B166" s="3">
+        <v>10163</v>
+      </c>
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
+      <c r="F166" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="H166" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="I166" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J166" s="3"/>
+      <c r="K166" s="2"/>
+      <c r="L166" s="2"/>
+      <c r="M166" s="2"/>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A167" s="3"/>
+      <c r="B167" s="3">
+        <v>10164</v>
+      </c>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3"/>
+      <c r="F167" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="H167" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="I167" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J167" s="3"/>
+      <c r="K167" s="2"/>
+      <c r="L167" s="2"/>
+      <c r="M167" s="2"/>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A168" s="3"/>
+      <c r="B168" s="3">
+        <v>10165</v>
+      </c>
+      <c r="C168" s="3"/>
+      <c r="D168" s="3"/>
+      <c r="F168" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="H168" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="I168" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J168" s="3"/>
+      <c r="K168" s="2"/>
+      <c r="L168" s="2"/>
+      <c r="M168" s="2"/>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A169" s="3"/>
+      <c r="B169" s="3">
+        <v>10166</v>
+      </c>
+      <c r="C169" s="3"/>
+      <c r="D169" s="3"/>
+      <c r="F169" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="H169" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="I169" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J169" s="3"/>
+      <c r="K169" s="2"/>
+      <c r="L169" s="2"/>
+      <c r="M169" s="2"/>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A170" s="3"/>
+      <c r="B170" s="3">
+        <v>10167</v>
+      </c>
+      <c r="C170" s="3"/>
+      <c r="D170" s="3"/>
+      <c r="F170" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="H170" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="I170" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J170" s="3"/>
+      <c r="K170" s="2"/>
+      <c r="L170" s="2"/>
+      <c r="M170" s="2"/>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A171" s="3"/>
+      <c r="B171" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C171" s="3"/>
+      <c r="D171" s="3"/>
+      <c r="F171" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="H171" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="I171" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J171" s="3"/>
+      <c r="K171" s="2"/>
+      <c r="L171" s="2"/>
+      <c r="M171" s="2"/>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A172" s="3"/>
+      <c r="B172" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="C172" s="3"/>
+      <c r="D172" s="3"/>
+      <c r="F172" s="3"/>
+      <c r="G172" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="H172" s="3"/>
+      <c r="I172" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="J172" s="3"/>
+      <c r="K172" s="2"/>
+      <c r="L172" s="2"/>
+      <c r="M172" s="2"/>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A173" s="3"/>
+      <c r="B173" s="3">
+        <v>10170</v>
+      </c>
+      <c r="C173" s="3"/>
+      <c r="D173" s="3"/>
+      <c r="F173" s="3"/>
+      <c r="G173" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="H173" s="3"/>
+      <c r="I173" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="J173" s="3"/>
+      <c r="K173" s="2"/>
+      <c r="L173" s="2"/>
+      <c r="M173" s="2"/>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A174" s="3"/>
+      <c r="B174" s="3">
+        <v>10171</v>
+      </c>
+      <c r="C174" s="3"/>
+      <c r="D174" s="3"/>
+      <c r="F174" s="3"/>
+      <c r="G174" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="H174" s="3"/>
+      <c r="I174" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="J174" s="3"/>
+      <c r="K174" s="2"/>
+      <c r="L174" s="2"/>
+      <c r="M174" s="2"/>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A175" s="3"/>
+      <c r="B175" s="3">
+        <v>10172</v>
+      </c>
+      <c r="C175" s="3"/>
+      <c r="D175" s="3"/>
+      <c r="F175" s="3"/>
+      <c r="G175" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="H175" s="3"/>
+      <c r="I175" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="J175" s="3"/>
+      <c r="K175" s="2"/>
+      <c r="L175" s="2"/>
+      <c r="M175" s="2"/>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A176" s="3"/>
+      <c r="B176" s="3">
+        <v>10173</v>
+      </c>
+      <c r="C176" s="3"/>
+      <c r="D176" s="3"/>
+      <c r="F176" s="3"/>
+      <c r="G176" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="H176" s="3"/>
+      <c r="I176" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="J176" s="3"/>
+      <c r="K176" s="2"/>
+      <c r="L176" s="2"/>
+      <c r="M176" s="2"/>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A177" s="3"/>
+      <c r="B177" s="3">
+        <v>10174</v>
+      </c>
+      <c r="C177" s="3"/>
+      <c r="D177" s="3"/>
+      <c r="F177" s="3"/>
+      <c r="G177" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="H177" s="3"/>
+      <c r="I177" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="J177" s="3"/>
+      <c r="K177" s="2"/>
+      <c r="L177" s="2"/>
+      <c r="M177" s="2"/>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A178" s="3"/>
+      <c r="B178" s="3">
+        <v>10175</v>
+      </c>
+      <c r="C178" s="3"/>
+      <c r="D178" s="3"/>
+      <c r="F178" s="3"/>
+      <c r="G178" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="H178" s="3"/>
+      <c r="I178" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="J178" s="3"/>
+      <c r="K178" s="2"/>
+      <c r="L178" s="2"/>
+      <c r="M178" s="2"/>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A179" s="3"/>
+      <c r="B179" s="3">
+        <v>10176</v>
+      </c>
+      <c r="C179" s="3"/>
+      <c r="D179" s="3"/>
+      <c r="F179" s="3"/>
+      <c r="G179" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="H179" s="3"/>
+      <c r="I179" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="J179" s="3"/>
+      <c r="K179" s="2"/>
+      <c r="L179" s="2"/>
+      <c r="M179" s="2"/>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A180" s="3"/>
+      <c r="B180" s="3">
+        <v>10177</v>
+      </c>
+      <c r="C180" s="3"/>
+      <c r="D180" s="3"/>
+      <c r="F180" s="3"/>
+      <c r="G180" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="H180" s="3"/>
+      <c r="I180" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="J180" s="3"/>
+      <c r="K180" s="2"/>
+      <c r="L180" s="2"/>
+      <c r="M180" s="2"/>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A181" s="3"/>
+      <c r="B181" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C181" s="3"/>
+      <c r="D181" s="3"/>
+      <c r="F181" s="3"/>
+      <c r="G181" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="H181" s="3"/>
+      <c r="I181" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J181" s="3"/>
+      <c r="K181" s="2"/>
+      <c r="L181" s="2"/>
+      <c r="M181" s="2"/>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A182" s="3"/>
+      <c r="B182" s="3">
+        <v>10179</v>
+      </c>
+      <c r="C182" s="3"/>
+      <c r="D182" s="3"/>
+      <c r="F182" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="H182" s="3"/>
+      <c r="I182" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J182" s="3"/>
+      <c r="K182" s="2"/>
+      <c r="L182" s="2"/>
+      <c r="M182" s="2"/>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A183" s="3"/>
+      <c r="B183" s="3">
+        <v>10180</v>
+      </c>
+      <c r="C183" s="3"/>
+      <c r="D183" s="3"/>
+      <c r="F183" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="G183" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="H183" s="3"/>
+      <c r="I183" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J183" s="3"/>
+      <c r="K183" s="2"/>
+      <c r="L183" s="2"/>
+      <c r="M183" s="2"/>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A184" s="3"/>
+      <c r="B184" s="3">
+        <v>10181</v>
+      </c>
+      <c r="C184" s="3"/>
+      <c r="D184" s="3"/>
+      <c r="F184" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="H184" s="3"/>
+      <c r="I184" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J184" s="3"/>
+      <c r="K184" s="2"/>
+      <c r="L184" s="2"/>
+      <c r="M184" s="2"/>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A185" s="3"/>
+      <c r="B185" s="3">
+        <v>10182</v>
+      </c>
+      <c r="C185" s="3"/>
+      <c r="D185" s="3"/>
+      <c r="F185" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="G185" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="H185" s="3"/>
+      <c r="I185" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J185" s="3"/>
+      <c r="K185" s="2"/>
+      <c r="L185" s="2"/>
+      <c r="M185" s="2"/>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A186" s="3"/>
+      <c r="B186" s="3">
+        <v>10183</v>
+      </c>
+      <c r="C186" s="3"/>
+      <c r="D186" s="3"/>
+      <c r="F186" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="H186" s="3"/>
+      <c r="I186" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J186" s="3"/>
+      <c r="K186" s="2"/>
+      <c r="L186" s="2"/>
+      <c r="M186" s="2"/>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A187" s="3"/>
+      <c r="B187" s="3">
+        <v>10184</v>
+      </c>
+      <c r="C187" s="3"/>
+      <c r="D187" s="3"/>
+      <c r="F187" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="H187" s="3"/>
+      <c r="I187" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J187" s="3"/>
+      <c r="K187" s="2"/>
+      <c r="L187" s="2"/>
+      <c r="M187" s="2"/>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A188" s="3"/>
+      <c r="B188" s="3">
+        <v>10185</v>
+      </c>
+      <c r="C188" s="3"/>
+      <c r="D188" s="3"/>
+      <c r="F188" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="H188" s="3"/>
+      <c r="I188" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J188" s="3"/>
+      <c r="K188" s="2"/>
+      <c r="L188" s="2"/>
+      <c r="M188" s="2"/>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A189" s="3"/>
+      <c r="B189" s="3">
+        <v>10186</v>
+      </c>
+      <c r="C189" s="3"/>
+      <c r="D189" s="3"/>
+      <c r="F189" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="H189" s="3"/>
+      <c r="I189" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J189" s="3"/>
+      <c r="K189" s="2"/>
+      <c r="L189" s="2"/>
+      <c r="M189" s="2"/>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A190" s="3"/>
+      <c r="B190" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="C190" s="3"/>
+      <c r="D190" s="3"/>
+      <c r="F190" s="3"/>
+      <c r="G190" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="H190" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="I190" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="J190" s="3"/>
+      <c r="K190" s="2"/>
+      <c r="L190" s="2"/>
+      <c r="M190" s="2"/>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A191" s="3"/>
+      <c r="B191" s="3">
+        <v>10188</v>
+      </c>
+      <c r="C191" s="3"/>
+      <c r="D191" s="3"/>
+      <c r="F191" s="3"/>
+      <c r="G191" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="H191" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="I191" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="J191" s="3"/>
+      <c r="K191" s="2"/>
+      <c r="L191" s="2"/>
+      <c r="M191" s="2"/>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A192" s="3"/>
+      <c r="B192" s="3">
+        <v>10189</v>
+      </c>
+      <c r="C192" s="3"/>
+      <c r="D192" s="3"/>
+      <c r="F192" s="3"/>
+      <c r="G192" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="H192" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="I192" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="J192" s="3"/>
+      <c r="K192" s="2"/>
+      <c r="L192" s="2"/>
+      <c r="M192" s="2"/>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A193" s="3"/>
+      <c r="B193" s="3">
+        <v>10190</v>
+      </c>
+      <c r="C193" s="3"/>
+      <c r="D193" s="3"/>
+      <c r="F193" s="3"/>
+      <c r="G193" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="H193" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="I193" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="J193" s="3"/>
+      <c r="K193" s="2"/>
+      <c r="L193" s="2"/>
+      <c r="M193" s="2"/>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A194" s="3"/>
+      <c r="B194" s="3">
+        <v>10191</v>
+      </c>
+      <c r="C194" s="3"/>
+      <c r="D194" s="3"/>
+      <c r="F194" s="3"/>
+      <c r="G194" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="H194" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="I194" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="J194" s="3"/>
+      <c r="K194" s="2"/>
+      <c r="L194" s="2"/>
+      <c r="M194" s="2"/>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A195" s="3"/>
+      <c r="B195" s="3">
+        <v>10192</v>
+      </c>
+      <c r="C195" s="3"/>
+      <c r="D195" s="3"/>
+      <c r="F195" s="3"/>
+      <c r="G195" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="H195" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="I195" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="J195" s="3"/>
+      <c r="K195" s="2"/>
+      <c r="L195" s="2"/>
+      <c r="M195" s="2"/>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A196" s="3"/>
+      <c r="B196" s="3">
+        <v>10193</v>
+      </c>
+      <c r="C196" s="3"/>
+      <c r="D196" s="3"/>
+      <c r="F196" s="3"/>
+      <c r="G196" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="H196" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="I196" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="J196" s="3"/>
+      <c r="K196" s="2"/>
+      <c r="L196" s="2"/>
+      <c r="M196" s="2"/>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A197" s="3"/>
+      <c r="B197" s="3">
+        <v>10194</v>
+      </c>
+      <c r="C197" s="3"/>
+      <c r="D197" s="3"/>
+      <c r="F197" s="3"/>
+      <c r="G197" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="H197" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="I197" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="J197" s="3"/>
+      <c r="K197" s="2"/>
+      <c r="L197" s="2"/>
+      <c r="M197" s="2"/>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A198" s="3"/>
+      <c r="B198" s="3">
+        <v>10195</v>
+      </c>
+      <c r="C198" s="3"/>
+      <c r="D198" s="3"/>
+      <c r="F198" s="3"/>
+      <c r="G198" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="H198" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="I198" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J198" s="3"/>
+      <c r="K198" s="2"/>
+      <c r="L198" s="2"/>
+      <c r="M198" s="2"/>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A199" s="3"/>
+      <c r="B199" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D199" s="3"/>
+      <c r="F199" s="3"/>
+      <c r="G199" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="H199" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="I199" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="J199" s="3"/>
+      <c r="K199" s="2"/>
+      <c r="L199" s="2"/>
+      <c r="M199" s="2"/>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A200" s="3"/>
+      <c r="B200" s="3">
+        <v>10197</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D200" s="3"/>
+      <c r="F200" s="3"/>
+      <c r="G200" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="H200" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="I200" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="J200" s="3"/>
+      <c r="K200" s="2"/>
+      <c r="L200" s="2"/>
+      <c r="M200" s="2"/>
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A201" s="3"/>
+      <c r="B201" s="3">
+        <v>10198</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D201" s="3"/>
+      <c r="F201" s="3"/>
+      <c r="G201" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="H201" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="I201" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="J201" s="3"/>
+      <c r="K201" s="2"/>
+      <c r="L201" s="2"/>
+      <c r="M201" s="2"/>
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A202" s="3"/>
+      <c r="B202" s="3">
+        <v>10199</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D202" s="3"/>
+      <c r="F202" s="3"/>
+      <c r="G202" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="H202" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="I202" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="J202" s="3"/>
+      <c r="K202" s="2"/>
+      <c r="L202" s="2"/>
+      <c r="M202" s="2"/>
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A203" s="3"/>
+      <c r="B203" s="3">
+        <v>10200</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="D203" s="3"/>
+      <c r="F203" s="3"/>
+      <c r="G203" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="H203" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="I203" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="J203" s="3"/>
+      <c r="K203" s="2"/>
+      <c r="L203" s="2"/>
+      <c r="M203" s="2"/>
+    </row>
+    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A204" s="3"/>
+      <c r="B204" s="3">
+        <v>10201</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D204" s="3"/>
+      <c r="F204" s="3"/>
+      <c r="G204" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="H204" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="I204" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="J204" s="3"/>
+      <c r="K204" s="2"/>
+      <c r="L204" s="2"/>
+      <c r="M204" s="2"/>
+    </row>
+    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A205" s="3"/>
+      <c r="B205" s="3">
+        <v>10202</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D205" s="3"/>
+      <c r="F205" s="3"/>
+      <c r="G205" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="H205" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="I205" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="J205" s="3"/>
+      <c r="K205" s="2"/>
+      <c r="L205" s="2"/>
+      <c r="M205" s="2"/>
+    </row>
+    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A206" s="3"/>
+      <c r="B206" s="3">
+        <v>10203</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D206" s="3"/>
+      <c r="F206" s="3"/>
+      <c r="G206" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="H206" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="I206" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="J206" s="3"/>
+      <c r="K206" s="2"/>
+      <c r="L206" s="2"/>
+      <c r="M206" s="2"/>
+    </row>
+    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A207" s="3"/>
+      <c r="B207" s="3">
+        <v>10204</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D207" s="3"/>
+      <c r="F207" s="3"/>
+      <c r="G207" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="H207" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="I207" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="J207" s="3"/>
+      <c r="K207" s="2"/>
+      <c r="L207" s="2"/>
+      <c r="M207" s="2"/>
+    </row>
+    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A208" s="3"/>
+      <c r="B208" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D208" s="3"/>
+      <c r="F208" s="3"/>
+      <c r="G208" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="H208" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="I208" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="J208" s="3"/>
+      <c r="K208" s="2"/>
+      <c r="L208" s="2"/>
+      <c r="M208" s="2"/>
+    </row>
+    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A209" s="3"/>
+      <c r="B209" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="C209" s="3"/>
+      <c r="D209" s="3"/>
+      <c r="F209" s="3"/>
+      <c r="G209" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="H209" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="I209" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="J209" s="3"/>
+      <c r="K209" s="2"/>
+      <c r="L209" s="2"/>
+      <c r="M209" s="2"/>
+    </row>
+    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A210" s="3"/>
+      <c r="B210" s="3">
+        <v>10207</v>
+      </c>
+      <c r="C210" s="3"/>
+      <c r="D210" s="3"/>
+      <c r="F210" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="H210" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="I210" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="J210" s="3"/>
+      <c r="K210" s="2"/>
+      <c r="L210" s="2"/>
+      <c r="M210" s="2"/>
+    </row>
+    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A211" s="3"/>
+      <c r="B211" s="3">
+        <v>10208</v>
+      </c>
+      <c r="C211" s="3"/>
+      <c r="D211" s="3"/>
+      <c r="F211" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="G211" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="H211" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="I211" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="J211" s="3"/>
+      <c r="K211" s="2"/>
+      <c r="L211" s="2"/>
+      <c r="M211" s="2"/>
+    </row>
+    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A212" s="3"/>
+      <c r="B212" s="3">
+        <v>10209</v>
+      </c>
+      <c r="C212" s="3"/>
+      <c r="D212" s="3"/>
+      <c r="F212" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G212" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="H212" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="I212" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="J212" s="3"/>
+      <c r="K212" s="2"/>
+      <c r="L212" s="2"/>
+      <c r="M212" s="2"/>
+    </row>
+    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A213" s="3"/>
+      <c r="B213" s="3">
+        <v>10210</v>
+      </c>
+      <c r="C213" s="3"/>
+      <c r="D213" s="3"/>
+      <c r="F213" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="G213" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="H213" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="I213" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="J213" s="3"/>
+      <c r="K213" s="2"/>
+      <c r="L213" s="2"/>
+      <c r="M213" s="2"/>
+    </row>
+    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A214" s="3"/>
+      <c r="B214" s="3">
+        <v>10211</v>
+      </c>
+      <c r="C214" s="3"/>
+      <c r="D214" s="3"/>
+      <c r="F214" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="H214" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="I214" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="J214" s="3"/>
+      <c r="K214" s="2"/>
+      <c r="L214" s="2"/>
+      <c r="M214" s="2"/>
+    </row>
+    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A215" s="3"/>
+      <c r="B215" s="3">
+        <v>10212</v>
+      </c>
+      <c r="C215" s="3"/>
+      <c r="D215" s="3"/>
+      <c r="F215" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G215" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="H215" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="I215" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="J215" s="3"/>
+      <c r="K215" s="2"/>
+      <c r="L215" s="2"/>
+      <c r="M215" s="2"/>
+    </row>
+    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A216" s="3"/>
+      <c r="B216" s="3">
+        <v>10213</v>
+      </c>
+      <c r="C216" s="3"/>
+      <c r="D216" s="3"/>
+      <c r="F216" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="H216" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="I216" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="J216" s="3"/>
+      <c r="K216" s="2"/>
+      <c r="L216" s="2"/>
+      <c r="M216" s="2"/>
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A217" s="3"/>
+      <c r="B217" s="3">
+        <v>10214</v>
+      </c>
+      <c r="C217" s="3"/>
+      <c r="D217" s="3"/>
+      <c r="F217" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G217" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="H217" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="I217" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="J217" s="3"/>
+      <c r="K217" s="2"/>
+      <c r="L217" s="2"/>
+      <c r="M217" s="2"/>
+    </row>
+    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A218" s="3"/>
+      <c r="B218" s="3">
+        <v>10215</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="D218" s="3"/>
+      <c r="F218" s="3"/>
+      <c r="G218" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H218" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="I218" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J218" s="3"/>
+      <c r="K218" s="2"/>
+      <c r="L218" s="2"/>
+      <c r="M218" s="2"/>
+    </row>
+    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A219" s="3"/>
+      <c r="B219" s="3">
+        <v>10216</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D219" s="3"/>
+      <c r="F219" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G219" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H219" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="I219" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J219" s="3"/>
+      <c r="K219" s="2"/>
+      <c r="L219" s="2"/>
+      <c r="M219" s="2"/>
+    </row>
+    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A220" s="3"/>
+      <c r="B220" s="3">
+        <v>10217</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D220" s="3"/>
+      <c r="F220" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G220" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H220" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="I220" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J220" s="3"/>
+      <c r="K220" s="2"/>
+      <c r="L220" s="2"/>
+      <c r="M220" s="2"/>
+    </row>
+    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A221" s="3"/>
+      <c r="B221" s="3">
+        <v>10218</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D221" s="3"/>
+      <c r="F221" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G221" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H221" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="I221" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J221" s="3"/>
+      <c r="K221" s="2"/>
+      <c r="L221" s="2"/>
+      <c r="M221" s="2"/>
+    </row>
+    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A222" s="3"/>
+      <c r="B222" s="3">
+        <v>10219</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D222" s="3"/>
+      <c r="F222" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G222" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H222" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="I222" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J222" s="3"/>
+      <c r="K222" s="2"/>
+      <c r="L222" s="2"/>
+      <c r="M222" s="2"/>
+    </row>
+    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A223" s="3"/>
+      <c r="B223" s="3">
+        <v>10220</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D223" s="3"/>
+      <c r="F223" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="G223" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H223" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="I223" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J223" s="3"/>
+      <c r="K223" s="2"/>
+      <c r="L223" s="2"/>
+      <c r="M223" s="2"/>
+    </row>
+    <row r="224" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A224" s="3"/>
+      <c r="B224" s="3">
+        <v>10221</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D224" s="3"/>
+      <c r="F224" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G224" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H224" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="I224" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J224" s="3"/>
+      <c r="K224" s="2"/>
+      <c r="L224" s="2"/>
+      <c r="M224" s="2"/>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A225" s="3"/>
+      <c r="B225" s="3">
+        <v>10222</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D225" s="3"/>
+      <c r="F225" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="G225" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H225" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="I225" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J225" s="3"/>
+      <c r="K225" s="2"/>
+      <c r="L225" s="2"/>
+      <c r="M225" s="2"/>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A226" s="3"/>
+      <c r="B226" s="3">
+        <v>10223</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D226" s="3"/>
+      <c r="F226" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G226" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="H226" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="I226" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J226" s="3"/>
+      <c r="K226" s="2"/>
+      <c r="L226" s="2"/>
+      <c r="M226" s="2"/>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A227" s="3"/>
+      <c r="B227" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D227" s="3"/>
+      <c r="F227" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="H227" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="I227" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="J227" s="3"/>
+      <c r="K227" s="2"/>
+      <c r="L227" s="2"/>
+      <c r="M227" s="2"/>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A228" s="3"/>
+      <c r="B228" s="3">
+        <v>10225</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="D228" s="3"/>
+      <c r="F228" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="H228" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="I228" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="J228" s="3"/>
+      <c r="K228" s="2"/>
+      <c r="L228" s="2"/>
+      <c r="M228" s="2"/>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A229" s="3"/>
+      <c r="B229" s="3">
+        <v>10226</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="D229" s="3"/>
+      <c r="F229" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="G229" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="H229" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="I229" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="J229" s="3"/>
+      <c r="K229" s="2"/>
+      <c r="L229" s="2"/>
+      <c r="M229" s="2"/>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A230" s="3"/>
+      <c r="B230" s="3">
+        <v>10227</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D230" s="3"/>
+      <c r="F230" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="H230" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="I230" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="J230" s="3"/>
+      <c r="K230" s="2"/>
+      <c r="L230" s="2"/>
+      <c r="M230" s="2"/>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A231" s="3"/>
+      <c r="B231" s="3">
+        <v>10228</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="D231" s="3"/>
+      <c r="F231" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="H231" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="I231" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="J231" s="3"/>
+      <c r="K231" s="2"/>
+      <c r="L231" s="2"/>
+      <c r="M231" s="2"/>
+    </row>
+    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A232" s="3"/>
+      <c r="B232" s="3">
+        <v>10229</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D232" s="3"/>
+      <c r="F232" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="G232" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="H232" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="I232" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="J232" s="3"/>
+      <c r="K232" s="2"/>
+      <c r="L232" s="2"/>
+      <c r="M232" s="2"/>
+    </row>
+    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A233" s="3"/>
+      <c r="B233" s="3">
+        <v>10230</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="D233" s="3"/>
+      <c r="F233" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="H233" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="I233" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="J233" s="3"/>
+      <c r="K233" s="2"/>
+      <c r="L233" s="2"/>
+      <c r="M233" s="2"/>
+    </row>
+    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A234" s="3"/>
+      <c r="B234" s="3">
+        <v>10231</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D234" s="3"/>
+      <c r="F234" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="H234" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="I234" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="J234" s="3"/>
+      <c r="K234" s="2"/>
+      <c r="L234" s="2"/>
+      <c r="M234" s="2"/>
+    </row>
+    <row r="235" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A235" s="3"/>
+      <c r="B235" s="3">
+        <v>10232</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D235" s="3"/>
+      <c r="F235" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G235" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="H235" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="I235" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="J235" s="3"/>
+      <c r="K235" s="2"/>
+      <c r="L235" s="2"/>
+      <c r="M235" s="2"/>
+    </row>
+    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A236" s="3"/>
+      <c r="B236" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="C236" s="3"/>
+      <c r="D236" s="3"/>
+      <c r="F236" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="H236" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I236" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="J236" s="3"/>
+      <c r="K236" s="2"/>
+      <c r="L236" s="2"/>
+      <c r="M236" s="2"/>
+    </row>
+    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A237" s="3"/>
+      <c r="B237" s="3">
+        <v>10234</v>
+      </c>
+      <c r="C237" s="3"/>
+      <c r="D237" s="3"/>
+      <c r="F237" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="H237" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I237" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="J237" s="3"/>
+      <c r="K237" s="2"/>
+      <c r="L237" s="2"/>
+      <c r="M237" s="2"/>
+    </row>
+    <row r="238" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A238" s="3"/>
+      <c r="B238" s="3">
+        <v>10235</v>
+      </c>
+      <c r="C238" s="3"/>
+      <c r="D238" s="3"/>
+      <c r="F238" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="H238" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I238" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="J238" s="3"/>
+      <c r="K238" s="2"/>
+      <c r="L238" s="2"/>
+      <c r="M238" s="2"/>
+    </row>
+    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A239" s="3"/>
+      <c r="B239" s="3">
+        <v>10236</v>
+      </c>
+      <c r="C239" s="3"/>
+      <c r="D239" s="3"/>
+      <c r="F239" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="G239" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="H239" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I239" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="J239" s="3"/>
+      <c r="K239" s="2"/>
+      <c r="L239" s="2"/>
+      <c r="M239" s="2"/>
+    </row>
+    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A240" s="3"/>
+      <c r="B240" s="3">
+        <v>10237</v>
+      </c>
+      <c r="C240" s="3"/>
+      <c r="D240" s="3"/>
+      <c r="F240" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="H240" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I240" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="J240" s="3"/>
+      <c r="K240" s="2"/>
+      <c r="L240" s="2"/>
+      <c r="M240" s="2"/>
+    </row>
+    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A241" s="3"/>
+      <c r="B241" s="3">
+        <v>10238</v>
+      </c>
+      <c r="C241" s="3"/>
+      <c r="D241" s="3"/>
+      <c r="F241" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="H241" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I241" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="J241" s="3"/>
+      <c r="K241" s="2"/>
+      <c r="L241" s="2"/>
+      <c r="M241" s="2"/>
+    </row>
+    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A242" s="3"/>
+      <c r="B242" s="3">
+        <v>10239</v>
+      </c>
+      <c r="C242" s="3"/>
+      <c r="D242" s="3"/>
+      <c r="F242" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="G242" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="H242" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I242" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="J242" s="3"/>
+      <c r="K242" s="2"/>
+      <c r="L242" s="2"/>
+      <c r="M242" s="2"/>
+    </row>
+    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A243" s="3"/>
+      <c r="B243" s="3">
+        <v>10240</v>
+      </c>
+      <c r="C243" s="3"/>
+      <c r="D243" s="3"/>
+      <c r="F243" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G243" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="H243" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I243" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="J243" s="3"/>
+      <c r="K243" s="2"/>
+      <c r="L243" s="2"/>
+      <c r="M243" s="2"/>
+    </row>
+    <row r="244" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A244" s="3"/>
+      <c r="B244" s="3">
+        <v>10241</v>
+      </c>
+      <c r="C244" s="3"/>
+      <c r="D244" s="3"/>
+      <c r="F244" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="G244" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="H244" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="I244" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="J244" s="3"/>
+      <c r="K244" s="2"/>
+      <c r="L244" s="2"/>
+      <c r="M244" s="2"/>
+    </row>
+    <row r="245" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A245" s="3"/>
+      <c r="B245" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C245" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D245" s="3"/>
+      <c r="F245" s="3"/>
+      <c r="G245" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="H245" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="I245" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="J245" s="3"/>
+      <c r="K245" s="2"/>
+      <c r="L245" s="2"/>
+      <c r="M245" s="2"/>
+    </row>
+    <row r="246" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A246" s="6"/>
+      <c r="B246" s="6">
+        <v>10243</v>
+      </c>
+      <c r="C246" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="D246" s="6"/>
+      <c r="F246" s="6"/>
+      <c r="G246" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="H246" s="6"/>
+      <c r="I246" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="J246" s="6"/>
+      <c r="K246" s="9"/>
+      <c r="L246" s="9"/>
+      <c r="M246" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Luban/Config/Datas/#TreasureConfig.xlsx
+++ b/Luban/Config/Datas/#TreasureConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93828D32-B3EB-480B-8928-079F9029C47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43EFB259-2035-46C9-8F30-F32EEDAD0CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="508">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -968,735 +968,745 @@
     <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成21伤害</t>
   </si>
   <si>
+    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成73伤害</t>
+  </si>
+  <si>
+    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成110伤害</t>
+  </si>
+  <si>
+    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成148伤害</t>
+  </si>
+  <si>
+    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成190伤害</t>
+  </si>
+  <si>
+    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成243伤害</t>
+  </si>
+  <si>
+    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成339伤害</t>
+  </si>
+  <si>
+    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成434伤害</t>
+  </si>
+  <si>
+    <t>精古开山刀</t>
+  </si>
+  <si>
+    <t>精古开山刀+1</t>
+  </si>
+  <si>
+    <t>武杀式命中后扣除目标240+GR*5体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
+  </si>
+  <si>
+    <t>精古开山刀+2</t>
+  </si>
+  <si>
+    <t>武杀式命中后扣除目标280+GR*5体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
+  </si>
+  <si>
+    <t>精古开山刀+3</t>
+  </si>
+  <si>
+    <t>武杀式命中后扣除目标280+GR*7体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
+  </si>
+  <si>
+    <t>精古开山刀+4</t>
+  </si>
+  <si>
+    <t>武杀式命中后扣除目标340+GR*7体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
+  </si>
+  <si>
+    <t>精古开山刀+5</t>
+  </si>
+  <si>
+    <t>精古开山刀+6</t>
+  </si>
+  <si>
+    <t>武杀式命中后扣除目标880+GR*9体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
+  </si>
+  <si>
+    <t>精古开山刀+7</t>
+  </si>
+  <si>
+    <t>武杀式命中后扣除目标880+GR*11体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
+  </si>
+  <si>
+    <t>精古开山刀+8</t>
+  </si>
+  <si>
+    <t>武杀式命中后扣除目标1122+GR*11体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
+  </si>
+  <si>
+    <t>姗岚幡</t>
+  </si>
+  <si>
+    <t>回合开始键的数量为10则获得1层回避状态</t>
+  </si>
+  <si>
+    <t>杀式造成的伤害增加，量为体的1.5%*招式威力</t>
+  </si>
+  <si>
+    <t>在排列行动的先后时，键的数量计算默认为8</t>
+  </si>
+  <si>
+    <t>渡梦舟+1</t>
+  </si>
+  <si>
+    <t>渡梦舟+2</t>
+  </si>
+  <si>
+    <t>渡梦舟+3</t>
+  </si>
+  <si>
+    <t>渡梦舟+4</t>
+  </si>
+  <si>
+    <t>渡梦舟+5</t>
+  </si>
+  <si>
+    <t>渡梦舟+6</t>
+  </si>
+  <si>
+    <t>渡梦舟+7</t>
+  </si>
+  <si>
+    <t>渡梦舟+8</t>
+  </si>
+  <si>
+    <t>拂容绫</t>
+  </si>
+  <si>
+    <t>技,6</t>
+  </si>
+  <si>
+    <t>战斗中角色至多持有3个异常状态</t>
+  </si>
+  <si>
+    <t>拂容绫+1</t>
+  </si>
+  <si>
+    <t>技,10</t>
+  </si>
+  <si>
+    <t>拂容绫+2</t>
+  </si>
+  <si>
+    <t>技,14</t>
+  </si>
+  <si>
+    <t>拂容绫+3</t>
+  </si>
+  <si>
+    <t>技,19.5</t>
+  </si>
+  <si>
+    <t>拂容绫+4</t>
+  </si>
+  <si>
+    <t>拂容绫+5</t>
+  </si>
+  <si>
+    <t>技,33.5</t>
+  </si>
+  <si>
+    <t>拂容绫+6</t>
+  </si>
+  <si>
+    <t>技,44.5</t>
+  </si>
+  <si>
+    <t>拂容绫+7</t>
+  </si>
+  <si>
+    <t>技,57.5</t>
+  </si>
+  <si>
+    <t>拂容绫+8</t>
+  </si>
+  <si>
+    <t>技,72.5</t>
+  </si>
+  <si>
+    <t>行动后目标在本回合对你的直接伤害减少20%</t>
+  </si>
+  <si>
+    <t>瘴珠</t>
+  </si>
+  <si>
+    <t>行动后获得一层毒瘴状态</t>
+  </si>
+  <si>
+    <t>绝世宝剑</t>
+  </si>
+  <si>
+    <t>对木桩造成的伤害提升999%</t>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Property</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ParamList</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=,),float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>额外参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Script</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>脚本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasureBase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.15,0.05,0.05,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.2,0.05,0.05,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.25,0.05,0.05,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.3,0.05,0.05,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.35,0.05,0.05,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.4,0.05,0.05,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.45,0.05,0.05,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5,0.05,0.05,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.55,0.05,0.05,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10070</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>38,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>57,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>68,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>84,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>130,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>160,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10079</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始随机消耗键直至不超过6个，每消耗一个键随机获得1层武增/术增/力增/技增</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,200011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10089</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10117</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10117</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>95</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>140</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>185</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>315</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>435</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>555</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10126</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10126</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10137</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10137</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10138</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10178</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10178</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10205</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10205</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10224</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10224</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10242</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10242</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10107</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用招式：掷物时，力的值以590替代，该效果该效果每2个回合可触发一次。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武杀式命中后扣除目标340+GR*9体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击精兽时倍率增加5百分比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杀式造成的伤害增加，量为体的1.5%*招式威力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05,0.15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05,0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05,0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05,0.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05,0.75</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05,0.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05,1.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05,1.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>125,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>125,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>132,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>132,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>158,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>158,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>400,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>510,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Feature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10098</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10098</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10131</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10168</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10169</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10169</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10187</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10187</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,500,5,21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,500,5,47</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,500,5,73</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,500,5,110</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,500,5,148</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,500,5,190</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,500,5,243</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,500,5,339</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,500,5,434</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10196</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10196</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240,3,3,0.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240,5,3,0.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>280,5,3,0.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>280,7,3,0.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>340,7,3,0.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>340,9,3,0.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>880,9,3,0.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>880,11,3,0.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1122,11,3,0.99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10206</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10206</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>渡梦舟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10233</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10233</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10160</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10160</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10112</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleTreasure10112</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成47伤害</t>
-  </si>
-  <si>
-    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成73伤害</t>
-  </si>
-  <si>
-    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成110伤害</t>
-  </si>
-  <si>
-    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成148伤害</t>
-  </si>
-  <si>
-    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成190伤害</t>
-  </si>
-  <si>
-    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成243伤害</t>
-  </si>
-  <si>
-    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成339伤害</t>
-  </si>
-  <si>
-    <t>受到鬼物的伤害减少30%，回合结束时全场角色消耗玄炁累计超过500则清空计数并5次对随机敌手造成434伤害</t>
-  </si>
-  <si>
-    <t>精古开山刀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>武杀式命中后扣除目标240+GR*3体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
-  </si>
-  <si>
-    <t>精古开山刀+1</t>
-  </si>
-  <si>
-    <t>武杀式命中后扣除目标240+GR*5体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
-  </si>
-  <si>
-    <t>精古开山刀+2</t>
-  </si>
-  <si>
-    <t>武杀式命中后扣除目标280+GR*5体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
-  </si>
-  <si>
-    <t>精古开山刀+3</t>
-  </si>
-  <si>
-    <t>武杀式命中后扣除目标280+GR*7体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
-  </si>
-  <si>
-    <t>精古开山刀+4</t>
-  </si>
-  <si>
-    <t>武杀式命中后扣除目标340+GR*7体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
-  </si>
-  <si>
-    <t>精古开山刀+5</t>
-  </si>
-  <si>
-    <t>精古开山刀+6</t>
-  </si>
-  <si>
-    <t>武杀式命中后扣除目标880+GR*9体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
-  </si>
-  <si>
-    <t>精古开山刀+7</t>
-  </si>
-  <si>
-    <t>武杀式命中后扣除目标880+GR*11体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
-  </si>
-  <si>
-    <t>精古开山刀+8</t>
-  </si>
-  <si>
-    <t>武杀式命中后扣除目标1122+GR*11体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
-  </si>
-  <si>
-    <t>姗岚幡</t>
-  </si>
-  <si>
-    <t>回合开始键的数量为10则获得1层回避状态</t>
-  </si>
-  <si>
-    <t>杀式造成的伤害增加，量为体的1.5%*招式威力</t>
-  </si>
-  <si>
-    <t>在排列行动的先后时，键的数量计算默认为8</t>
-  </si>
-  <si>
-    <t>渡梦舟+1</t>
-  </si>
-  <si>
-    <t>渡梦舟+2</t>
-  </si>
-  <si>
-    <t>渡梦舟+3</t>
-  </si>
-  <si>
-    <t>渡梦舟+4</t>
-  </si>
-  <si>
-    <t>渡梦舟+5</t>
-  </si>
-  <si>
-    <t>渡梦舟+6</t>
-  </si>
-  <si>
-    <t>渡梦舟+7</t>
-  </si>
-  <si>
-    <t>渡梦舟+8</t>
-  </si>
-  <si>
-    <t>拂容绫</t>
-  </si>
-  <si>
-    <t>技,6</t>
-  </si>
-  <si>
-    <t>战斗中角色至多持有3个异常状态</t>
-  </si>
-  <si>
-    <t>拂容绫+1</t>
-  </si>
-  <si>
-    <t>技,10</t>
-  </si>
-  <si>
-    <t>拂容绫+2</t>
-  </si>
-  <si>
-    <t>技,14</t>
-  </si>
-  <si>
-    <t>拂容绫+3</t>
-  </si>
-  <si>
-    <t>技,19.5</t>
-  </si>
-  <si>
-    <t>拂容绫+4</t>
-  </si>
-  <si>
-    <t>拂容绫+5</t>
-  </si>
-  <si>
-    <t>技,33.5</t>
-  </si>
-  <si>
-    <t>拂容绫+6</t>
-  </si>
-  <si>
-    <t>技,44.5</t>
-  </si>
-  <si>
-    <t>拂容绫+7</t>
-  </si>
-  <si>
-    <t>技,57.5</t>
-  </si>
-  <si>
-    <t>拂容绫+8</t>
-  </si>
-  <si>
-    <t>技,72.5</t>
-  </si>
-  <si>
-    <t>行动后目标在本回合对你的直接伤害减少20%</t>
-  </si>
-  <si>
-    <t>瘴珠</t>
-  </si>
-  <si>
-    <t>行动后获得一层毒瘴状态</t>
-  </si>
-  <si>
-    <t>绝世宝剑</t>
-  </si>
-  <si>
-    <t>对木桩造成的伤害提升999%</t>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Property</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>属性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ParamList</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(list#sep=,),float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>额外参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Script</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>脚本</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasureBase</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.15,0.05,0.05,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.2,0.05,0.05,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.25,0.05,0.05,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.3,0.05,0.05,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.35,0.05,0.05,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.4,0.05,0.05,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.45,0.05,0.05,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.5,0.05,0.05,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.55,0.05,0.05,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10070</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>30,2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>38,2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46,2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>57,2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>68,2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>84,2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100,2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>130,2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>160,2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10079</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合开始随机消耗键直至不超过6个，每消耗一个键随机获得1层武增/术增/力增/技增</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6,200011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10089</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10117</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10117</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>60</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>95</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>140</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>185</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>250</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>315</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>435</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>555</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10126</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10126</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10137</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10137</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10138</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10178</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10178</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10205</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10205</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10224</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10224</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10242</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10242</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.18</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.21</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10107</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用招式：掷物时，力的值以590替代，该效果该效果每2个回合可触发一次。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武杀式命中后扣除目标340+GR*9体，三个回合内只会触发一次，若目标体高于99%则不进入冷却</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击精兽时倍率增加5百分比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>杀式造成的伤害增加，量为体的1.5%*招式威力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.05,0.15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.05,0.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.05,0.45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.05,0.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.05,0.75</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.05,0.9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.05,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10025</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.05,1.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.05,1.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>125,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>125,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>132,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>132,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>158,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>158,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>400,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>400,5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>510,5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Feature</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>特性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10098</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10098</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10131</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10168</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10169</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10169</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10187</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10187</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3,500,5,21</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3,500,5,47</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3,500,5,73</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3,500,5,110</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3,500,5,148</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3,500,5,190</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3,500,5,243</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3,500,5,339</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3,500,5,434</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10196</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10196</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>240,3,3,0.99</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>240,5,3,0.99</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>280,5,3,0.99</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>280,7,3,0.99</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>340,7,3,0.99</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>340,9,3,0.99</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>880,9,3,0.99</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>880,11,3,0.99</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1122,11,3,0.99</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.015</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10206</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10206</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>渡梦舟</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10233</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10233</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10160</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10160</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10112</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleTreasure10112</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10215</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2137,22 +2147,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -2178,7 +2188,7 @@
         <v>4</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -2192,22 +2202,22 @@
         <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="33" x14ac:dyDescent="0.2">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="49.5" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
       <c r="B4" s="3">
         <v>10001</v>
@@ -2218,7 +2228,7 @@
       <c r="D4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="4" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="5" t="s">
@@ -2242,10 +2252,10 @@
       <c r="D5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>377</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>379</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>12</v>
@@ -2268,10 +2278,10 @@
       <c r="D6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>15</v>
@@ -2292,10 +2302,10 @@
       <c r="D7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>17</v>
@@ -2316,10 +2326,10 @@
       <c r="D8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>19</v>
@@ -2340,10 +2350,10 @@
       <c r="D9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>21</v>
@@ -2364,10 +2374,10 @@
       <c r="D10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>23</v>
@@ -2388,10 +2398,10 @@
       <c r="D11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>25</v>
@@ -2412,10 +2422,10 @@
       <c r="D12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>27</v>
@@ -2436,10 +2446,10 @@
       <c r="D13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>29</v>
@@ -2460,13 +2470,13 @@
       <c r="D14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="2"/>
@@ -2484,10 +2494,10 @@
       <c r="D15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>32</v>
@@ -2508,10 +2518,10 @@
       <c r="D16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>444</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>446</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>34</v>
@@ -2532,10 +2542,10 @@
       <c r="D17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>36</v>
@@ -2556,10 +2566,10 @@
       <c r="D18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>38</v>
@@ -2580,10 +2590,10 @@
       <c r="D19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>40</v>
@@ -2604,10 +2614,10 @@
       <c r="D20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>42</v>
@@ -2628,10 +2638,10 @@
       <c r="D21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>44</v>
@@ -2652,10 +2662,10 @@
       <c r="D22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>46</v>
@@ -2676,7 +2686,7 @@
       <c r="D23" s="6"/>
       <c r="F23" s="6"/>
       <c r="G23" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
@@ -2698,7 +2708,7 @@
       <c r="D24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
@@ -2718,7 +2728,7 @@
       <c r="D25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
@@ -2738,7 +2748,7 @@
       <c r="D26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
@@ -2758,7 +2768,7 @@
       <c r="D27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
@@ -2778,10 +2788,10 @@
       <c r="D28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>54</v>
@@ -2800,10 +2810,10 @@
       <c r="D29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>55</v>
@@ -2822,10 +2832,10 @@
       <c r="D30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>56</v>
@@ -2844,10 +2854,10 @@
       <c r="D31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>57</v>
@@ -2866,10 +2876,10 @@
       <c r="D32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>58</v>
@@ -2888,10 +2898,10 @@
       <c r="D33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>59</v>
@@ -2910,10 +2920,10 @@
       <c r="D34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>60</v>
@@ -2932,10 +2942,10 @@
       <c r="D35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>61</v>
@@ -2954,10 +2964,10 @@
       <c r="D36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>62</v>
@@ -2978,7 +2988,7 @@
       <c r="D37" s="6"/>
       <c r="F37" s="6"/>
       <c r="G37" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
@@ -2998,7 +3008,7 @@
       <c r="D38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
@@ -3016,11 +3026,11 @@
         <v>65</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3" t="s">
@@ -3040,11 +3050,11 @@
         <v>67</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3" t="s">
@@ -3064,11 +3074,11 @@
         <v>69</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3" t="s">
@@ -3088,11 +3098,11 @@
         <v>71</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3" t="s">
@@ -3112,11 +3122,11 @@
         <v>73</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3" t="s">
@@ -3136,11 +3146,11 @@
         <v>75</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3" t="s">
@@ -3160,11 +3170,11 @@
         <v>77</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3" t="s">
@@ -3184,11 +3194,11 @@
         <v>79</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3" t="s">
@@ -3208,11 +3218,11 @@
         <v>81</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3" t="s">
@@ -3236,7 +3246,7 @@
         <v>84</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H48" s="6"/>
       <c r="I48" s="6"/>
@@ -3258,7 +3268,7 @@
         <v>86</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H49" s="6"/>
       <c r="I49" s="6"/>
@@ -3280,7 +3290,7 @@
         <v>88</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H50" s="6"/>
       <c r="I50" s="6"/>
@@ -3302,7 +3312,7 @@
         <v>90</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H51" s="6"/>
       <c r="I51" s="6"/>
@@ -3324,7 +3334,7 @@
         <v>92</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H52" s="6"/>
       <c r="I52" s="6"/>
@@ -3346,7 +3356,7 @@
         <v>94</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H53" s="6"/>
       <c r="I53" s="6"/>
@@ -3368,7 +3378,7 @@
         <v>96</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
@@ -3390,7 +3400,7 @@
         <v>98</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H55" s="6"/>
       <c r="I55" s="6"/>
@@ -3412,7 +3422,7 @@
         <v>100</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H56" s="6"/>
       <c r="I56" s="6"/>
@@ -3434,7 +3444,7 @@
         <v>102</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H57" s="6"/>
       <c r="I57" s="6"/>
@@ -3456,7 +3466,7 @@
         <v>104</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H58" s="6"/>
       <c r="I58" s="6"/>
@@ -3478,7 +3488,7 @@
         <v>106</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H59" s="6"/>
       <c r="I59" s="6"/>
@@ -3500,7 +3510,7 @@
         <v>108</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H60" s="6"/>
       <c r="I60" s="6"/>
@@ -3522,7 +3532,7 @@
         <v>110</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H61" s="6"/>
       <c r="I61" s="6"/>
@@ -3544,7 +3554,7 @@
         <v>112</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H62" s="6"/>
       <c r="I62" s="6"/>
@@ -3566,7 +3576,7 @@
         <v>114</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H63" s="6"/>
       <c r="I63" s="6"/>
@@ -3588,7 +3598,7 @@
         <v>116</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
@@ -3610,7 +3620,7 @@
         <v>118</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
@@ -3632,7 +3642,7 @@
         <v>120</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
@@ -3654,7 +3664,7 @@
         <v>122</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
@@ -3676,7 +3686,7 @@
         <v>124</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
@@ -3698,7 +3708,7 @@
         <v>126</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
@@ -3720,7 +3730,7 @@
         <v>128</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
@@ -3742,7 +3752,7 @@
         <v>130</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
@@ -3764,7 +3774,7 @@
         <v>132</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
@@ -3784,10 +3794,10 @@
       <c r="D73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>134</v>
@@ -3810,10 +3820,10 @@
         <v>136</v>
       </c>
       <c r="G74" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="H74" s="3" t="s">
         <v>388</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>390</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>137</v>
@@ -3836,10 +3846,10 @@
         <v>139</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>140</v>
@@ -3862,10 +3872,10 @@
         <v>142</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>143</v>
@@ -3888,10 +3898,10 @@
         <v>145</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>146</v>
@@ -3914,10 +3924,10 @@
         <v>148</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>149</v>
@@ -3940,10 +3950,10 @@
         <v>151</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>152</v>
@@ -3966,10 +3976,10 @@
         <v>154</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>155</v>
@@ -3992,10 +4002,10 @@
         <v>157</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>158</v>
@@ -4018,13 +4028,13 @@
         <v>160</v>
       </c>
       <c r="G82" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="H82" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="H82" s="3" t="s">
-        <v>400</v>
-      </c>
       <c r="I82" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J82" s="3"/>
       <c r="K82" s="2"/>
@@ -4044,10 +4054,10 @@
         <v>163</v>
       </c>
       <c r="G83" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="H83" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>400</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>161</v>
@@ -4070,10 +4080,10 @@
         <v>165</v>
       </c>
       <c r="G84" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="H84" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>400</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>161</v>
@@ -4096,10 +4106,10 @@
         <v>167</v>
       </c>
       <c r="G85" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="H85" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>400</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>161</v>
@@ -4122,10 +4132,10 @@
         <v>169</v>
       </c>
       <c r="G86" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="H86" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>400</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>161</v>
@@ -4148,10 +4158,10 @@
         <v>171</v>
       </c>
       <c r="G87" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="H87" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>400</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>161</v>
@@ -4174,10 +4184,10 @@
         <v>173</v>
       </c>
       <c r="G88" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="H88" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>400</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>161</v>
@@ -4200,10 +4210,10 @@
         <v>175</v>
       </c>
       <c r="G89" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="H89" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>400</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>161</v>
@@ -4226,10 +4236,10 @@
         <v>177</v>
       </c>
       <c r="G90" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="H90" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>400</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>161</v>
@@ -4248,7 +4258,7 @@
       <c r="D91" s="6"/>
       <c r="F91" s="6"/>
       <c r="G91" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H91" s="6"/>
       <c r="I91" s="6" t="s">
@@ -4270,10 +4280,10 @@
         <v>179</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>180</v>
@@ -4294,10 +4304,10 @@
         <v>181</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>180</v>
@@ -4318,10 +4328,10 @@
         <v>182</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>180</v>
@@ -4342,10 +4352,10 @@
         <v>183</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>180</v>
@@ -4366,10 +4376,10 @@
         <v>114</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>180</v>
@@ -4390,10 +4400,10 @@
         <v>184</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>180</v>
@@ -4414,10 +4424,10 @@
         <v>185</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>180</v>
@@ -4438,10 +4448,10 @@
         <v>186</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>180</v>
@@ -4462,10 +4472,10 @@
         <v>187</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>180</v>
@@ -4478,7 +4488,7 @@
     <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="3"/>
       <c r="B101" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>188</v>
@@ -4488,7 +4498,7 @@
         <v>189</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H101" s="3"/>
       <c r="I101" s="3" t="s">
@@ -4512,7 +4522,7 @@
         <v>192</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H102" s="3"/>
       <c r="I102" s="3" t="s">
@@ -4536,7 +4546,7 @@
         <v>194</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H103" s="3"/>
       <c r="I103" s="3" t="s">
@@ -4560,7 +4570,7 @@
         <v>196</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H104" s="3"/>
       <c r="I104" s="3" t="s">
@@ -4584,7 +4594,7 @@
         <v>160</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H105" s="3"/>
       <c r="I105" s="3" t="s">
@@ -4608,7 +4618,7 @@
         <v>199</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H106" s="3"/>
       <c r="I106" s="3" t="s">
@@ -4632,7 +4642,7 @@
         <v>201</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H107" s="3"/>
       <c r="I107" s="3" t="s">
@@ -4656,7 +4666,7 @@
         <v>203</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H108" s="3"/>
       <c r="I108" s="3" t="s">
@@ -4680,7 +4690,7 @@
         <v>205</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H109" s="3"/>
       <c r="I109" s="3" t="s">
@@ -4704,10 +4714,10 @@
         <v>207</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>208</v>
@@ -4730,10 +4740,10 @@
         <v>210</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>211</v>
@@ -4756,10 +4766,10 @@
         <v>213</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>214</v>
@@ -4782,10 +4792,10 @@
         <v>216</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>217</v>
@@ -4808,10 +4818,10 @@
         <v>219</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>220</v>
@@ -4824,16 +4834,16 @@
     <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" s="3"/>
       <c r="B115" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="F115" s="3"/>
       <c r="G115" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>221</v>
@@ -4852,10 +4862,10 @@
       <c r="D116" s="3"/>
       <c r="F116" s="3"/>
       <c r="G116" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>221</v>
@@ -4874,10 +4884,10 @@
       <c r="D117" s="3"/>
       <c r="F117" s="3"/>
       <c r="G117" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>221</v>
@@ -4896,10 +4906,10 @@
       <c r="D118" s="3"/>
       <c r="F118" s="3"/>
       <c r="G118" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>221</v>
@@ -4918,10 +4928,10 @@
       <c r="D119" s="3"/>
       <c r="F119" s="3"/>
       <c r="G119" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>221</v>
@@ -4934,16 +4944,16 @@
     <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120" s="3"/>
       <c r="B120" s="3" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="F120" s="3"/>
       <c r="G120" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>222</v>
@@ -4962,10 +4972,10 @@
       <c r="D121" s="3"/>
       <c r="F121" s="3"/>
       <c r="G121" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="H121" s="3" t="s">
         <v>404</v>
-      </c>
-      <c r="H121" s="3" t="s">
-        <v>406</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>223</v>
@@ -4984,10 +4994,10 @@
       <c r="D122" s="3"/>
       <c r="F122" s="3"/>
       <c r="G122" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>224</v>
@@ -5006,10 +5016,10 @@
       <c r="D123" s="3"/>
       <c r="F123" s="3"/>
       <c r="G123" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="I123" s="3" t="s">
         <v>225</v>
@@ -5028,10 +5038,10 @@
       <c r="D124" s="3"/>
       <c r="F124" s="3"/>
       <c r="G124" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>226</v>
@@ -5050,10 +5060,10 @@
       <c r="D125" s="3"/>
       <c r="F125" s="3"/>
       <c r="G125" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>227</v>
@@ -5072,10 +5082,10 @@
       <c r="D126" s="3"/>
       <c r="F126" s="3"/>
       <c r="G126" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>228</v>
@@ -5094,10 +5104,10 @@
       <c r="D127" s="3"/>
       <c r="F127" s="3"/>
       <c r="G127" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>229</v>
@@ -5116,10 +5126,10 @@
       <c r="D128" s="3"/>
       <c r="F128" s="3"/>
       <c r="G128" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>230</v>
@@ -5132,16 +5142,16 @@
     <row r="129" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A129" s="3"/>
       <c r="B129" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="F129" s="3"/>
       <c r="G129" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>231</v>
@@ -5160,10 +5170,10 @@
       <c r="D130" s="3"/>
       <c r="F130" s="3"/>
       <c r="G130" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H130" s="3" t="s">
         <v>415</v>
-      </c>
-      <c r="H130" s="3" t="s">
-        <v>417</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>232</v>
@@ -5182,10 +5192,10 @@
       <c r="D131" s="3"/>
       <c r="F131" s="3"/>
       <c r="G131" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I131" s="3" t="s">
         <v>233</v>
@@ -5204,10 +5214,10 @@
       <c r="D132" s="3"/>
       <c r="F132" s="3"/>
       <c r="G132" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="I132" s="3" t="s">
         <v>234</v>
@@ -5226,10 +5236,10 @@
       <c r="D133" s="3"/>
       <c r="F133" s="3"/>
       <c r="G133" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>235</v>
@@ -5250,10 +5260,10 @@
       <c r="D134" s="3"/>
       <c r="F134" s="3"/>
       <c r="G134" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I134" s="3" t="s">
         <v>237</v>
@@ -5276,7 +5286,7 @@
         <v>239</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H135" s="6"/>
       <c r="I135" s="6"/>
@@ -5298,7 +5308,7 @@
         <v>241</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H136" s="6"/>
       <c r="I136" s="6"/>
@@ -5320,7 +5330,7 @@
         <v>243</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H137" s="6"/>
       <c r="I137" s="6"/>
@@ -5342,7 +5352,7 @@
         <v>245</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H138" s="6"/>
       <c r="I138" s="6"/>
@@ -5364,7 +5374,7 @@
         <v>247</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H139" s="6"/>
       <c r="I139" s="6"/>
@@ -5376,7 +5386,7 @@
     <row r="140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A140" s="3"/>
       <c r="B140" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>248</v>
@@ -5384,10 +5394,10 @@
       <c r="D140" s="3"/>
       <c r="F140" s="3"/>
       <c r="G140" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I140" s="3" t="s">
         <v>249</v>
@@ -5400,7 +5410,7 @@
     <row r="141" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A141" s="3"/>
       <c r="B141" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>250</v>
@@ -5410,10 +5420,10 @@
         <v>251</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I141" s="3" t="s">
         <v>249</v>
@@ -5436,10 +5446,10 @@
         <v>253</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I142" s="3" t="s">
         <v>249</v>
@@ -5462,10 +5472,10 @@
         <v>255</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I143" s="3" t="s">
         <v>249</v>
@@ -5488,10 +5498,10 @@
         <v>257</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I144" s="3" t="s">
         <v>249</v>
@@ -5514,10 +5524,10 @@
         <v>259</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I145" s="3" t="s">
         <v>249</v>
@@ -5540,10 +5550,10 @@
         <v>261</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I146" s="3" t="s">
         <v>249</v>
@@ -5566,10 +5576,10 @@
         <v>263</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I147" s="3" t="s">
         <v>249</v>
@@ -5592,10 +5602,10 @@
         <v>265</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I148" s="3" t="s">
         <v>249</v>
@@ -5617,7 +5627,7 @@
       <c r="E149" s="7"/>
       <c r="F149" s="6"/>
       <c r="G149" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H149" s="6"/>
       <c r="I149" s="6" t="s">
@@ -5640,11 +5650,11 @@
       <c r="E150" s="7"/>
       <c r="F150" s="6"/>
       <c r="G150" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H150" s="6"/>
       <c r="I150" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="J150" s="3"/>
       <c r="K150" s="2"/>
@@ -5663,7 +5673,7 @@
       <c r="E151" s="7"/>
       <c r="F151" s="6"/>
       <c r="G151" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H151" s="6"/>
       <c r="I151" s="6" t="s">
@@ -5686,7 +5696,7 @@
       <c r="E152" s="7"/>
       <c r="F152" s="6"/>
       <c r="G152" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H152" s="6"/>
       <c r="I152" s="6" t="s">
@@ -5709,7 +5719,7 @@
       <c r="E153" s="7"/>
       <c r="F153" s="6"/>
       <c r="G153" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H153" s="6"/>
       <c r="I153" s="6" t="s">
@@ -5732,7 +5742,7 @@
       <c r="E154" s="7"/>
       <c r="F154" s="6"/>
       <c r="G154" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H154" s="6"/>
       <c r="I154" s="6" t="s">
@@ -5755,7 +5765,7 @@
       <c r="E155" s="7"/>
       <c r="F155" s="6"/>
       <c r="G155" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H155" s="6"/>
       <c r="I155" s="6" t="s">
@@ -5778,7 +5788,7 @@
       <c r="E156" s="7"/>
       <c r="F156" s="6"/>
       <c r="G156" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H156" s="6"/>
       <c r="I156" s="6" t="s">
@@ -5801,7 +5811,7 @@
       <c r="E157" s="7"/>
       <c r="F157" s="6"/>
       <c r="G157" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H157" s="6"/>
       <c r="I157" s="6" t="s">
@@ -5823,7 +5833,7 @@
         <v>283</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H158" s="6"/>
       <c r="I158" s="6"/>
@@ -5843,7 +5853,7 @@
         <v>284</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H159" s="6"/>
       <c r="I159" s="6"/>
@@ -5863,7 +5873,7 @@
         <v>285</v>
       </c>
       <c r="G160" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H160" s="6"/>
       <c r="I160" s="6"/>
@@ -5883,7 +5893,7 @@
         <v>286</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H161" s="6"/>
       <c r="I161" s="6"/>
@@ -5903,7 +5913,7 @@
         <v>287</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H162" s="6"/>
       <c r="I162" s="6"/>
@@ -5915,7 +5925,7 @@
     <row r="163" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A163" s="3"/>
       <c r="B163" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
@@ -5923,10 +5933,10 @@
         <v>288</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I163" s="3" t="s">
         <v>289</v>
@@ -5947,10 +5957,10 @@
         <v>290</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I164" s="3" t="s">
         <v>289</v>
@@ -5971,10 +5981,10 @@
         <v>291</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I165" s="3" t="s">
         <v>289</v>
@@ -5995,10 +6005,10 @@
         <v>292</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I166" s="3" t="s">
         <v>289</v>
@@ -6019,10 +6029,10 @@
         <v>84</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I167" s="3" t="s">
         <v>289</v>
@@ -6043,10 +6053,10 @@
         <v>293</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I168" s="3" t="s">
         <v>289</v>
@@ -6067,10 +6077,10 @@
         <v>294</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I169" s="3" t="s">
         <v>289</v>
@@ -6091,10 +6101,10 @@
         <v>295</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H170" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I170" s="3" t="s">
         <v>289</v>
@@ -6107,7 +6117,7 @@
     <row r="171" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A171" s="3"/>
       <c r="B171" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
@@ -6115,10 +6125,10 @@
         <v>296</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H171" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I171" s="3" t="s">
         <v>289</v>
@@ -6131,13 +6141,13 @@
     <row r="172" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A172" s="3"/>
       <c r="B172" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="F172" s="3"/>
       <c r="G172" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H172" s="3"/>
       <c r="I172" s="3" t="s">
@@ -6157,7 +6167,7 @@
       <c r="D173" s="3"/>
       <c r="F173" s="3"/>
       <c r="G173" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H173" s="3"/>
       <c r="I173" s="3" t="s">
@@ -6177,7 +6187,7 @@
       <c r="D174" s="3"/>
       <c r="F174" s="3"/>
       <c r="G174" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H174" s="3"/>
       <c r="I174" s="3" t="s">
@@ -6197,7 +6207,7 @@
       <c r="D175" s="3"/>
       <c r="F175" s="3"/>
       <c r="G175" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H175" s="3"/>
       <c r="I175" s="3" t="s">
@@ -6217,7 +6227,7 @@
       <c r="D176" s="3"/>
       <c r="F176" s="3"/>
       <c r="G176" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H176" s="3"/>
       <c r="I176" s="3" t="s">
@@ -6237,7 +6247,7 @@
       <c r="D177" s="3"/>
       <c r="F177" s="3"/>
       <c r="G177" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H177" s="3"/>
       <c r="I177" s="3" t="s">
@@ -6257,7 +6267,7 @@
       <c r="D178" s="3"/>
       <c r="F178" s="3"/>
       <c r="G178" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H178" s="3"/>
       <c r="I178" s="3" t="s">
@@ -6277,7 +6287,7 @@
       <c r="D179" s="3"/>
       <c r="F179" s="3"/>
       <c r="G179" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H179" s="3"/>
       <c r="I179" s="3" t="s">
@@ -6297,7 +6307,7 @@
       <c r="D180" s="3"/>
       <c r="F180" s="3"/>
       <c r="G180" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H180" s="3"/>
       <c r="I180" s="3" t="s">
@@ -6311,13 +6321,13 @@
     <row r="181" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A181" s="3"/>
       <c r="B181" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="F181" s="3"/>
       <c r="G181" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H181" s="3"/>
       <c r="I181" s="3" t="s">
@@ -6339,7 +6349,7 @@
         <v>299</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H182" s="3"/>
       <c r="I182" s="3" t="s">
@@ -6361,7 +6371,7 @@
         <v>300</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H183" s="3"/>
       <c r="I183" s="3" t="s">
@@ -6383,7 +6393,7 @@
         <v>301</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H184" s="3"/>
       <c r="I184" s="3" t="s">
@@ -6405,7 +6415,7 @@
         <v>302</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H185" s="3"/>
       <c r="I185" s="3" t="s">
@@ -6427,7 +6437,7 @@
         <v>303</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H186" s="3"/>
       <c r="I186" s="3" t="s">
@@ -6449,7 +6459,7 @@
         <v>304</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H187" s="3"/>
       <c r="I187" s="3" t="s">
@@ -6471,7 +6481,7 @@
         <v>305</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H188" s="3"/>
       <c r="I188" s="3" t="s">
@@ -6493,7 +6503,7 @@
         <v>306</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H189" s="3"/>
       <c r="I189" s="3" t="s">
@@ -6507,16 +6517,16 @@
     <row r="190" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A190" s="3"/>
       <c r="B190" s="3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="F190" s="3"/>
       <c r="G190" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="I190" s="3" t="s">
         <v>307</v>
@@ -6535,13 +6545,13 @@
       <c r="D191" s="3"/>
       <c r="F191" s="3"/>
       <c r="G191" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="H191" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="H191" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="I191" s="3" t="s">
-        <v>308</v>
+        <v>504</v>
       </c>
       <c r="J191" s="3"/>
       <c r="K191" s="2"/>
@@ -6557,13 +6567,13 @@
       <c r="D192" s="3"/>
       <c r="F192" s="3"/>
       <c r="G192" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I192" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J192" s="3"/>
       <c r="K192" s="2"/>
@@ -6579,13 +6589,13 @@
       <c r="D193" s="3"/>
       <c r="F193" s="3"/>
       <c r="G193" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="I193" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J193" s="3"/>
       <c r="K193" s="2"/>
@@ -6601,13 +6611,13 @@
       <c r="D194" s="3"/>
       <c r="F194" s="3"/>
       <c r="G194" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="H194" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="I194" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J194" s="3"/>
       <c r="K194" s="2"/>
@@ -6623,13 +6633,13 @@
       <c r="D195" s="3"/>
       <c r="F195" s="3"/>
       <c r="G195" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="H195" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="I195" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J195" s="3"/>
       <c r="K195" s="2"/>
@@ -6645,13 +6655,13 @@
       <c r="D196" s="3"/>
       <c r="F196" s="3"/>
       <c r="G196" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="H196" s="3" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="I196" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J196" s="3"/>
       <c r="K196" s="2"/>
@@ -6667,13 +6677,13 @@
       <c r="D197" s="3"/>
       <c r="F197" s="3"/>
       <c r="G197" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="H197" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="I197" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J197" s="3"/>
       <c r="K197" s="2"/>
@@ -6689,13 +6699,13 @@
       <c r="D198" s="3"/>
       <c r="F198" s="3"/>
       <c r="G198" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="H198" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="I198" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J198" s="3"/>
       <c r="K198" s="2"/>
@@ -6705,21 +6715,21 @@
     <row r="199" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A199" s="3"/>
       <c r="B199" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D199" s="3"/>
       <c r="F199" s="3"/>
       <c r="G199" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H199" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="I199" s="3" t="s">
-        <v>317</v>
+        <v>505</v>
       </c>
       <c r="J199" s="3"/>
       <c r="K199" s="2"/>
@@ -6732,18 +6742,18 @@
         <v>10197</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D200" s="3"/>
       <c r="F200" s="3"/>
       <c r="G200" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="H200" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="H200" s="3" t="s">
-        <v>486</v>
-      </c>
       <c r="I200" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J200" s="3"/>
       <c r="K200" s="2"/>
@@ -6756,18 +6766,18 @@
         <v>10198</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D201" s="3"/>
       <c r="F201" s="3"/>
       <c r="G201" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I201" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J201" s="3"/>
       <c r="K201" s="2"/>
@@ -6780,18 +6790,18 @@
         <v>10199</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D202" s="3"/>
       <c r="F202" s="3"/>
       <c r="G202" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="I202" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="J202" s="3"/>
       <c r="K202" s="2"/>
@@ -6804,18 +6814,18 @@
         <v>10200</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D203" s="3"/>
       <c r="F203" s="3"/>
       <c r="G203" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H203" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="I203" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="J203" s="3"/>
       <c r="K203" s="2"/>
@@ -6828,18 +6838,18 @@
         <v>10201</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D204" s="3"/>
       <c r="F204" s="3"/>
       <c r="G204" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="I204" s="3" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="J204" s="3"/>
       <c r="K204" s="2"/>
@@ -6852,18 +6862,18 @@
         <v>10202</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D205" s="3"/>
       <c r="F205" s="3"/>
       <c r="G205" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="I205" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="J205" s="3"/>
       <c r="K205" s="2"/>
@@ -6876,18 +6886,18 @@
         <v>10203</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D206" s="3"/>
       <c r="F206" s="3"/>
       <c r="G206" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H206" s="3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="I206" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="J206" s="3"/>
       <c r="K206" s="2"/>
@@ -6900,18 +6910,18 @@
         <v>10204</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D207" s="3"/>
       <c r="F207" s="3"/>
       <c r="G207" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="I207" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J207" s="3"/>
       <c r="K207" s="2"/>
@@ -6921,21 +6931,21 @@
     <row r="208" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A208" s="3"/>
       <c r="B208" s="3" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D208" s="3"/>
       <c r="F208" s="3"/>
       <c r="G208" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="H208" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="I208" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="J208" s="3"/>
       <c r="K208" s="2"/>
@@ -6945,19 +6955,19 @@
     <row r="209" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A209" s="3"/>
       <c r="B209" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="F209" s="3"/>
       <c r="G209" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H209" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="I209" s="3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="J209" s="3"/>
       <c r="K209" s="2"/>
@@ -6975,13 +6985,13 @@
         <v>299</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H210" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="I210" s="3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="J210" s="3"/>
       <c r="K210" s="2"/>
@@ -6999,13 +7009,13 @@
         <v>300</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H211" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="I211" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J211" s="3"/>
       <c r="K211" s="2"/>
@@ -7023,13 +7033,13 @@
         <v>301</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="I212" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J212" s="3"/>
       <c r="K212" s="2"/>
@@ -7047,13 +7057,13 @@
         <v>302</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H213" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="I213" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J213" s="3"/>
       <c r="K213" s="2"/>
@@ -7071,13 +7081,13 @@
         <v>303</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H214" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="I214" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J214" s="3"/>
       <c r="K214" s="2"/>
@@ -7095,13 +7105,13 @@
         <v>304</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H215" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="I215" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J215" s="3"/>
       <c r="K215" s="2"/>
@@ -7119,13 +7129,13 @@
         <v>305</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="I216" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J216" s="3"/>
       <c r="K216" s="2"/>
@@ -7143,13 +7153,13 @@
         <v>306</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H217" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="I217" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J217" s="3"/>
       <c r="K217" s="2"/>
@@ -7158,22 +7168,24 @@
     </row>
     <row r="218" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A218" s="3"/>
-      <c r="B218" s="3">
-        <v>10215</v>
+      <c r="B218" s="3" t="s">
+        <v>506</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="D218" s="3"/>
+        <v>495</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>507</v>
+      </c>
       <c r="F218" s="3"/>
       <c r="G218" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H218" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="I218" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="J218" s="3"/>
       <c r="K218" s="2"/>
@@ -7186,20 +7198,22 @@
         <v>10216</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D219" s="3"/>
+        <v>335</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>507</v>
+      </c>
       <c r="F219" s="3" t="s">
         <v>251</v>
       </c>
       <c r="G219" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H219" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="I219" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="J219" s="3"/>
       <c r="K219" s="2"/>
@@ -7212,20 +7226,22 @@
         <v>10217</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="D220" s="3"/>
+        <v>336</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>507</v>
+      </c>
       <c r="F220" s="3" t="s">
         <v>253</v>
       </c>
       <c r="G220" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H220" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="I220" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="J220" s="3"/>
       <c r="K220" s="2"/>
@@ -7238,20 +7254,22 @@
         <v>10218</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="D221" s="3"/>
+        <v>337</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>507</v>
+      </c>
       <c r="F221" s="3" t="s">
         <v>255</v>
       </c>
       <c r="G221" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H221" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="I221" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="J221" s="3"/>
       <c r="K221" s="2"/>
@@ -7264,20 +7282,22 @@
         <v>10219</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="D222" s="3"/>
+        <v>338</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>507</v>
+      </c>
       <c r="F222" s="3" t="s">
         <v>257</v>
       </c>
       <c r="G222" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H222" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="I222" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="J222" s="3"/>
       <c r="K222" s="2"/>
@@ -7290,20 +7310,22 @@
         <v>10220</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="D223" s="3"/>
+        <v>339</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>507</v>
+      </c>
       <c r="F223" s="3" t="s">
         <v>259</v>
       </c>
       <c r="G223" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H223" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="I223" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="J223" s="3"/>
       <c r="K223" s="2"/>
@@ -7316,20 +7338,22 @@
         <v>10221</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="D224" s="3"/>
+        <v>340</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>507</v>
+      </c>
       <c r="F224" s="3" t="s">
         <v>261</v>
       </c>
       <c r="G224" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H224" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="I224" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="J224" s="3"/>
       <c r="K224" s="2"/>
@@ -7342,20 +7366,22 @@
         <v>10222</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="D225" s="3"/>
+        <v>341</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>507</v>
+      </c>
       <c r="F225" s="3" t="s">
         <v>263</v>
       </c>
       <c r="G225" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H225" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="I225" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="J225" s="3"/>
       <c r="K225" s="2"/>
@@ -7368,20 +7394,22 @@
         <v>10223</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="D226" s="3"/>
+        <v>342</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>507</v>
+      </c>
       <c r="F226" s="3" t="s">
         <v>265</v>
       </c>
       <c r="G226" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H226" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="I226" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="J226" s="3"/>
       <c r="K226" s="2"/>
@@ -7391,23 +7419,23 @@
     <row r="227" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A227" s="3"/>
       <c r="B227" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D227" s="3"/>
       <c r="F227" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H227" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I227" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J227" s="3"/>
       <c r="K227" s="2"/>
@@ -7420,20 +7448,20 @@
         <v>10225</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D228" s="3"/>
       <c r="F228" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I228" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J228" s="3"/>
       <c r="K228" s="2"/>
@@ -7446,20 +7474,20 @@
         <v>10226</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D229" s="3"/>
       <c r="F229" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I229" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J229" s="3"/>
       <c r="K229" s="2"/>
@@ -7472,20 +7500,20 @@
         <v>10227</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D230" s="3"/>
       <c r="F230" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H230" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I230" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J230" s="3"/>
       <c r="K230" s="2"/>
@@ -7498,20 +7526,20 @@
         <v>10228</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D231" s="3"/>
       <c r="F231" s="3" t="s">
         <v>104</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H231" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I231" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J231" s="3"/>
       <c r="K231" s="2"/>
@@ -7524,20 +7552,20 @@
         <v>10229</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D232" s="3"/>
       <c r="F232" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H232" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I232" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J232" s="3"/>
       <c r="K232" s="2"/>
@@ -7550,20 +7578,20 @@
         <v>10230</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D233" s="3"/>
       <c r="F233" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H233" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I233" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J233" s="3"/>
       <c r="K233" s="2"/>
@@ -7576,20 +7604,20 @@
         <v>10231</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D234" s="3"/>
       <c r="F234" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H234" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I234" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J234" s="3"/>
       <c r="K234" s="2"/>
@@ -7602,20 +7630,20 @@
         <v>10232</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D235" s="3"/>
       <c r="F235" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H235" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I235" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J235" s="3"/>
       <c r="K235" s="2"/>
@@ -7625,7 +7653,7 @@
     <row r="236" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A236" s="3"/>
       <c r="B236" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
@@ -7633,13 +7661,13 @@
         <v>288</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="H236" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I236" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J236" s="3"/>
       <c r="K236" s="2"/>
@@ -7657,13 +7685,13 @@
         <v>290</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="H237" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I237" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J237" s="3"/>
       <c r="K237" s="2"/>
@@ -7681,13 +7709,13 @@
         <v>291</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="H238" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I238" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J238" s="3"/>
       <c r="K238" s="2"/>
@@ -7705,13 +7733,13 @@
         <v>292</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="H239" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I239" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J239" s="3"/>
       <c r="K239" s="2"/>
@@ -7729,13 +7757,13 @@
         <v>84</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="H240" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I240" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J240" s="3"/>
       <c r="K240" s="2"/>
@@ -7753,13 +7781,13 @@
         <v>293</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="H241" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I241" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J241" s="3"/>
       <c r="K241" s="2"/>
@@ -7777,13 +7805,13 @@
         <v>294</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="H242" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I242" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J242" s="3"/>
       <c r="K242" s="2"/>
@@ -7801,13 +7829,13 @@
         <v>295</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="H243" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I243" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J243" s="3"/>
       <c r="K243" s="2"/>
@@ -7825,13 +7853,13 @@
         <v>296</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="H244" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I244" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J244" s="3"/>
       <c r="K244" s="2"/>
@@ -7841,21 +7869,21 @@
     <row r="245" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A245" s="3"/>
       <c r="B245" s="3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D245" s="3"/>
       <c r="F245" s="3"/>
       <c r="G245" s="3" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H245" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I245" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="J245" s="3"/>
       <c r="K245" s="2"/>
@@ -7868,16 +7896,16 @@
         <v>10243</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D246" s="6"/>
       <c r="F246" s="6"/>
       <c r="G246" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H246" s="6"/>
       <c r="I246" s="6" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="J246" s="6"/>
       <c r="K246" s="9"/>

--- a/Luban/Config/Datas/#TreasureConfig.xlsx
+++ b/Luban/Config/Datas/#TreasureConfig.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43EFB259-2035-46C9-8F30-F32EEDAD0CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
